--- a/research/traditional_assets/database/data/greece/greece_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_farming_agriculture.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="atse_spir" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04849999999999999</v>
+        <v>0.0286</v>
       </c>
       <c r="G2">
-        <v>-0.004790419161676645</v>
+        <v>0.114792899408284</v>
       </c>
       <c r="H2">
-        <v>-0.04167664670658683</v>
+        <v>0.07396449704142012</v>
       </c>
       <c r="I2">
-        <v>-0.03095808383233533</v>
+        <v>0.02011834319526628</v>
       </c>
       <c r="J2">
-        <v>-0.03095808383233533</v>
+        <v>0.02011834319526628</v>
       </c>
       <c r="K2">
-        <v>-0.698</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.04179640718562874</v>
+        <v>-0.004970414201183433</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.511</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
-        <v>0.1125550660792951</v>
+        <v>0.3128119800332779</v>
       </c>
       <c r="W2">
-        <v>-0.3793478260869565</v>
+        <v>-0.03888888888888889</v>
       </c>
       <c r="X2">
-        <v>0.3303631038630176</v>
+        <v>0.1909532678815458</v>
       </c>
       <c r="Y2">
-        <v>-0.7097109299499742</v>
+        <v>-0.2298421567704347</v>
       </c>
       <c r="Z2">
-        <v>0.7978977544194935</v>
+        <v>0.9971089739807657</v>
       </c>
       <c r="AA2">
-        <v>-0.02470138557095079</v>
+        <v>0.02006018054162487</v>
       </c>
       <c r="AB2">
-        <v>0.1351499349278877</v>
+        <v>0.09733114487379287</v>
       </c>
       <c r="AC2">
-        <v>-0.1598513204988385</v>
+        <v>-0.07727096433216799</v>
       </c>
       <c r="AD2">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="AG2">
-        <v>14.789</v>
+        <v>14.52</v>
       </c>
       <c r="AH2">
-        <v>0.7711693548387097</v>
+        <v>0.7318161535029005</v>
       </c>
       <c r="AI2">
-        <v>0.8762886597938144</v>
+        <v>0.8728046833422033</v>
       </c>
       <c r="AJ2">
-        <v>0.7651197682239123</v>
+        <v>0.7072576716999512</v>
       </c>
       <c r="AK2">
-        <v>0.8725588530296773</v>
+        <v>0.8586635127143701</v>
       </c>
       <c r="AL2">
-        <v>1.4</v>
+        <v>0.922</v>
       </c>
       <c r="AM2">
-        <v>-2.08</v>
+        <v>-1.068</v>
       </c>
       <c r="AN2">
-        <v>58.62068965517241</v>
+        <v>12.61538461538461</v>
       </c>
       <c r="AO2">
-        <v>-0.3692857142857143</v>
+        <v>0.368763557483731</v>
       </c>
       <c r="AP2">
-        <v>56.66283524904215</v>
+        <v>11.16923076923077</v>
       </c>
       <c r="AQ2">
-        <v>0.2485576923076923</v>
+        <v>-0.3183520599250936</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04849999999999999</v>
+        <v>0.0286</v>
       </c>
       <c r="G3">
-        <v>-0.004790419161676645</v>
+        <v>0.114792899408284</v>
       </c>
       <c r="H3">
-        <v>-0.04167664670658683</v>
+        <v>0.07396449704142012</v>
       </c>
       <c r="I3">
-        <v>-0.03095808383233533</v>
+        <v>0.02011834319526628</v>
       </c>
       <c r="J3">
-        <v>-0.03095808383233533</v>
+        <v>0.02011834319526628</v>
       </c>
       <c r="K3">
-        <v>-0.698</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.04179640718562874</v>
+        <v>-0.004970414201183433</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.511</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>0.1125550660792951</v>
+        <v>0.3128119800332779</v>
       </c>
       <c r="W3">
-        <v>-0.3793478260869565</v>
+        <v>-0.03888888888888889</v>
       </c>
       <c r="X3">
-        <v>0.3303631038630176</v>
+        <v>0.1909532678815458</v>
       </c>
       <c r="Y3">
-        <v>-0.7097109299499742</v>
+        <v>-0.2298421567704347</v>
       </c>
       <c r="Z3">
-        <v>0.7978977544194935</v>
+        <v>0.9971089739807657</v>
       </c>
       <c r="AA3">
-        <v>-0.02470138557095079</v>
+        <v>0.02006018054162487</v>
       </c>
       <c r="AB3">
-        <v>0.1351499349278877</v>
+        <v>0.09733114487379287</v>
       </c>
       <c r="AC3">
-        <v>-0.1598513204988385</v>
+        <v>-0.07727096433216799</v>
       </c>
       <c r="AD3">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="AG3">
-        <v>14.789</v>
+        <v>14.52</v>
       </c>
       <c r="AH3">
-        <v>0.7711693548387097</v>
+        <v>0.7318161535029005</v>
       </c>
       <c r="AI3">
-        <v>0.8762886597938144</v>
+        <v>0.8728046833422033</v>
       </c>
       <c r="AJ3">
-        <v>0.7651197682239123</v>
+        <v>0.7072576716999512</v>
       </c>
       <c r="AK3">
-        <v>0.8725588530296773</v>
+        <v>0.8586635127143701</v>
       </c>
       <c r="AL3">
-        <v>1.4</v>
+        <v>0.922</v>
       </c>
       <c r="AM3">
-        <v>-2.08</v>
+        <v>-1.068</v>
       </c>
       <c r="AN3">
-        <v>58.62068965517241</v>
+        <v>12.61538461538461</v>
       </c>
       <c r="AO3">
-        <v>-0.3692857142857143</v>
+        <v>0.368763557483731</v>
       </c>
       <c r="AP3">
-        <v>56.66283524904215</v>
+        <v>11.16923076923077</v>
       </c>
       <c r="AQ3">
-        <v>0.2485576923076923</v>
+        <v>-0.3183520599250936</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The House of Agriculture Spiroy S.A. (ATSE:SPIR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATSE:SPIR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.368763557483731</v>
+      </c>
+      <c r="F2">
+        <v>4.63791212055834</v>
+      </c>
+      <c r="G2">
+        <v>12.6153846153846</v>
+      </c>
+      <c r="H2">
+        <v>5.34392307692308</v>
+      </c>
+      <c r="I2">
+        <v>0.731816153502901</v>
+      </c>
+      <c r="J2">
+        <v>0.31</v>
+      </c>
+      <c r="K2">
+        <v>6.01</v>
+      </c>
+      <c r="L2">
+        <v>21.2859045461156</v>
+      </c>
+      <c r="M2">
+        <v>20.53</v>
+      </c>
+      <c r="N2">
+        <v>26.3530045461156</v>
+      </c>
+      <c r="O2">
+        <v>16.4</v>
+      </c>
+      <c r="P2">
+        <v>6.9471</v>
+      </c>
+      <c r="Q2">
+        <v>0.09733114487379289</v>
+      </c>
+      <c r="R2">
+        <v>0.0843980039071517</v>
+      </c>
+      <c r="S2">
+        <v>0.0630220619910736</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.190953267881546</v>
+      </c>
+      <c r="X2">
+        <v>0.104478817256742</v>
+      </c>
+      <c r="Y2">
+        <v>1.84175834131814</v>
+      </c>
+      <c r="Z2">
+        <v>0.795017492655409</v>
+      </c>
+      <c r="AA2">
+        <v>16.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.08079751537317134</v>
+      </c>
+      <c r="AC2">
+        <v>0.3687635574837311</v>
+      </c>
+      <c r="AD2">
+        <v>16.4</v>
+      </c>
+      <c r="AE2">
+        <v>0.922</v>
+      </c>
+      <c r="AF2">
+        <v>0.96</v>
+      </c>
+      <c r="AG2">
+        <v>1.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>6.01</v>
+      </c>
+      <c r="AK2">
+        <v>0.08261304671092226</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.019</v>
+      </c>
+      <c r="AR2">
+        <v>0.922</v>
+      </c>
+      <c r="AS2">
+        <v>16.4</v>
+      </c>
+      <c r="AT2">
+        <v>1.88</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08743531219913256</v>
+      </c>
+      <c r="C2">
+        <v>26.58724150672563</v>
+      </c>
+      <c r="D2">
+        <v>24.70724150672563</v>
+      </c>
+      <c r="E2">
+        <v>-16.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.88</v>
+      </c>
+      <c r="H2">
+        <v>6.01</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.6</v>
+      </c>
+      <c r="K2">
+        <v>0.96</v>
+      </c>
+      <c r="L2">
+        <v>1.64</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.64</v>
+      </c>
+      <c r="O2">
+        <v>0.3608</v>
+      </c>
+      <c r="P2">
+        <v>1.2792</v>
+      </c>
+      <c r="Q2">
+        <v>2.2392</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08743531219913256</v>
+      </c>
+      <c r="T2">
+        <v>0.5887122450442502</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08728897451229446</v>
+      </c>
+      <c r="C3">
+        <v>26.43770692302099</v>
+      </c>
+      <c r="D3">
+        <v>24.78180692302099</v>
+      </c>
+      <c r="E3">
+        <v>-16.1759</v>
+      </c>
+      <c r="F3">
+        <v>0.2241</v>
+      </c>
+      <c r="G3">
+        <v>1.88</v>
+      </c>
+      <c r="H3">
+        <v>6.01</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.6</v>
+      </c>
+      <c r="K3">
+        <v>0.96</v>
+      </c>
+      <c r="L3">
+        <v>1.64</v>
+      </c>
+      <c r="M3">
+        <v>0.01001727</v>
+      </c>
+      <c r="N3">
+        <v>1.62998273</v>
+      </c>
+      <c r="O3">
+        <v>0.3585962006</v>
+      </c>
+      <c r="P3">
+        <v>1.2713865294</v>
+      </c>
+      <c r="Q3">
+        <v>2.2313865294</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08781849950736814</v>
+      </c>
+      <c r="T3">
+        <v>0.5933505839445988</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>163.7172602914766</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08714263682545638</v>
+      </c>
+      <c r="C4">
+        <v>26.28862377230616</v>
+      </c>
+      <c r="D4">
+        <v>24.85682377230616</v>
+      </c>
+      <c r="E4">
+        <v>-15.9518</v>
+      </c>
+      <c r="F4">
+        <v>0.4481999999999999</v>
+      </c>
+      <c r="G4">
+        <v>1.88</v>
+      </c>
+      <c r="H4">
+        <v>6.01</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.6</v>
+      </c>
+      <c r="K4">
+        <v>0.96</v>
+      </c>
+      <c r="L4">
+        <v>1.64</v>
+      </c>
+      <c r="M4">
+        <v>0.02003454</v>
+      </c>
+      <c r="N4">
+        <v>1.61996546</v>
+      </c>
+      <c r="O4">
+        <v>0.3563924012</v>
+      </c>
+      <c r="P4">
+        <v>1.2635730588</v>
+      </c>
+      <c r="Q4">
+        <v>2.2235730588</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08820950696475141</v>
+      </c>
+      <c r="T4">
+        <v>0.5980835828225056</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>81.85863014573832</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.0869962991386183</v>
+      </c>
+      <c r="C5">
+        <v>26.13999616661842</v>
+      </c>
+      <c r="D5">
+        <v>24.93229616661842</v>
+      </c>
+      <c r="E5">
+        <v>-15.7277</v>
+      </c>
+      <c r="F5">
+        <v>0.6722999999999999</v>
+      </c>
+      <c r="G5">
+        <v>1.88</v>
+      </c>
+      <c r="H5">
+        <v>6.01</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.6</v>
+      </c>
+      <c r="K5">
+        <v>0.96</v>
+      </c>
+      <c r="L5">
+        <v>1.64</v>
+      </c>
+      <c r="M5">
+        <v>0.03005181</v>
+      </c>
+      <c r="N5">
+        <v>1.60994819</v>
+      </c>
+      <c r="O5">
+        <v>0.3541886018</v>
+      </c>
+      <c r="P5">
+        <v>1.2557595882</v>
+      </c>
+      <c r="Q5">
+        <v>2.2157595882</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08860857643156525</v>
+      </c>
+      <c r="T5">
+        <v>0.6029141693061425</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>54.57242009715888</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.0868499614517802</v>
+      </c>
+      <c r="C6">
+        <v>25.9918282680884</v>
+      </c>
+      <c r="D6">
+        <v>25.0082282680884</v>
+      </c>
+      <c r="E6">
+        <v>-15.5036</v>
+      </c>
+      <c r="F6">
+        <v>0.8963999999999999</v>
+      </c>
+      <c r="G6">
+        <v>1.88</v>
+      </c>
+      <c r="H6">
+        <v>6.01</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.6</v>
+      </c>
+      <c r="K6">
+        <v>0.96</v>
+      </c>
+      <c r="L6">
+        <v>1.64</v>
+      </c>
+      <c r="M6">
+        <v>0.04006908</v>
+      </c>
+      <c r="N6">
+        <v>1.59993092</v>
+      </c>
+      <c r="O6">
+        <v>0.3519848024</v>
+      </c>
+      <c r="P6">
+        <v>1.2479461176</v>
+      </c>
+      <c r="Q6">
+        <v>2.2079461176</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08901595984560437</v>
+      </c>
+      <c r="T6">
+        <v>0.6078453930081884</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>40.92931507286916</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08670362376494212</v>
+      </c>
+      <c r="C7">
+        <v>25.84412428970522</v>
+      </c>
+      <c r="D7">
+        <v>25.08462428970522</v>
+      </c>
+      <c r="E7">
+        <v>-15.2795</v>
+      </c>
+      <c r="F7">
+        <v>1.1205</v>
+      </c>
+      <c r="G7">
+        <v>1.88</v>
+      </c>
+      <c r="H7">
+        <v>6.01</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.6</v>
+      </c>
+      <c r="K7">
+        <v>0.96</v>
+      </c>
+      <c r="L7">
+        <v>1.64</v>
+      </c>
+      <c r="M7">
+        <v>0.05008634999999999</v>
+      </c>
+      <c r="N7">
+        <v>1.58991365</v>
+      </c>
+      <c r="O7">
+        <v>0.349781003</v>
+      </c>
+      <c r="P7">
+        <v>1.240132647</v>
+      </c>
+      <c r="Q7">
+        <v>2.200132647</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08943191975257064</v>
+      </c>
+      <c r="T7">
+        <v>0.6128804319460669</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>32.74345205829533</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08655728607810402</v>
+      </c>
+      <c r="C8">
+        <v>25.69688849609573</v>
+      </c>
+      <c r="D8">
+        <v>25.16148849609574</v>
+      </c>
+      <c r="E8">
+        <v>-15.0554</v>
+      </c>
+      <c r="F8">
+        <v>1.3446</v>
+      </c>
+      <c r="G8">
+        <v>1.88</v>
+      </c>
+      <c r="H8">
+        <v>6.01</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.6</v>
+      </c>
+      <c r="K8">
+        <v>0.96</v>
+      </c>
+      <c r="L8">
+        <v>1.64</v>
+      </c>
+      <c r="M8">
+        <v>0.06010362</v>
+      </c>
+      <c r="N8">
+        <v>1.57989638</v>
+      </c>
+      <c r="O8">
+        <v>0.3475772036000001</v>
+      </c>
+      <c r="P8">
+        <v>1.2323191764</v>
+      </c>
+      <c r="Q8">
+        <v>2.1923191764</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08985672987032342</v>
+      </c>
+      <c r="T8">
+        <v>0.6180225993719852</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.28621004857944</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08641094839126592</v>
+      </c>
+      <c r="C9">
+        <v>25.55012520431803</v>
+      </c>
+      <c r="D9">
+        <v>25.23882520431803</v>
+      </c>
+      <c r="E9">
+        <v>-14.8313</v>
+      </c>
+      <c r="F9">
+        <v>1.5687</v>
+      </c>
+      <c r="G9">
+        <v>1.88</v>
+      </c>
+      <c r="H9">
+        <v>6.01</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.6</v>
+      </c>
+      <c r="K9">
+        <v>0.96</v>
+      </c>
+      <c r="L9">
+        <v>1.64</v>
+      </c>
+      <c r="M9">
+        <v>0.07012089000000001</v>
+      </c>
+      <c r="N9">
+        <v>1.56987911</v>
+      </c>
+      <c r="O9">
+        <v>0.3453734042</v>
+      </c>
+      <c r="P9">
+        <v>1.2245057058</v>
+      </c>
+      <c r="Q9">
+        <v>2.1845057058</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09029067568953325</v>
+      </c>
+      <c r="T9">
+        <v>0.6232753510436224</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.38818004163952</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08626461070442783</v>
+      </c>
+      <c r="C10">
+        <v>25.40383878466973</v>
+      </c>
+      <c r="D10">
+        <v>25.31663878466973</v>
+      </c>
+      <c r="E10">
+        <v>-14.6072</v>
+      </c>
+      <c r="F10">
+        <v>1.7928</v>
+      </c>
+      <c r="G10">
+        <v>1.88</v>
+      </c>
+      <c r="H10">
+        <v>6.01</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.6</v>
+      </c>
+      <c r="K10">
+        <v>0.96</v>
+      </c>
+      <c r="L10">
+        <v>1.64</v>
+      </c>
+      <c r="M10">
+        <v>0.08013816</v>
+      </c>
+      <c r="N10">
+        <v>1.55986184</v>
+      </c>
+      <c r="O10">
+        <v>0.3431696048</v>
+      </c>
+      <c r="P10">
+        <v>1.2166922352</v>
+      </c>
+      <c r="Q10">
+        <v>2.1766922352</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0907340551135085</v>
+      </c>
+      <c r="T10">
+        <v>0.6286422929689907</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.46465753643458</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08611827301758974</v>
+      </c>
+      <c r="C11">
+        <v>25.25803366151121</v>
+      </c>
+      <c r="D11">
+        <v>25.39493366151121</v>
+      </c>
+      <c r="E11">
+        <v>-14.3831</v>
+      </c>
+      <c r="F11">
+        <v>2.0169</v>
+      </c>
+      <c r="G11">
+        <v>1.88</v>
+      </c>
+      <c r="H11">
+        <v>6.01</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.6</v>
+      </c>
+      <c r="K11">
+        <v>0.96</v>
+      </c>
+      <c r="L11">
+        <v>1.64</v>
+      </c>
+      <c r="M11">
+        <v>0.09015542999999999</v>
+      </c>
+      <c r="N11">
+        <v>1.54984457</v>
+      </c>
+      <c r="O11">
+        <v>0.3409658054</v>
+      </c>
+      <c r="P11">
+        <v>1.2088787646</v>
+      </c>
+      <c r="Q11">
+        <v>2.1688787646</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0911871791402085</v>
+      </c>
+      <c r="T11">
+        <v>0.6341271896619496</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.034866</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.19080669905296</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08597193533075165</v>
+      </c>
+      <c r="C12">
+        <v>25.11271431410423</v>
+      </c>
+      <c r="D12">
+        <v>25.47371431410423</v>
+      </c>
+      <c r="E12">
+        <v>-14.159</v>
+      </c>
+      <c r="F12">
+        <v>2.241</v>
+      </c>
+      <c r="G12">
+        <v>1.88</v>
+      </c>
+      <c r="H12">
+        <v>6.01</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.6</v>
+      </c>
+      <c r="K12">
+        <v>0.96</v>
+      </c>
+      <c r="L12">
+        <v>1.64</v>
+      </c>
+      <c r="M12">
+        <v>0.1001727</v>
+      </c>
+      <c r="N12">
+        <v>1.5398273</v>
+      </c>
+      <c r="O12">
+        <v>0.3387620060000001</v>
+      </c>
+      <c r="P12">
+        <v>1.201065294</v>
+      </c>
+      <c r="Q12">
+        <v>2.161065294</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09165037258972404</v>
+      </c>
+      <c r="T12">
+        <v>0.6397339729480852</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.034866</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.37172602914767</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08582559764391356</v>
+      </c>
+      <c r="C13">
+        <v>24.96788527746609</v>
+      </c>
+      <c r="D13">
+        <v>25.55298527746609</v>
+      </c>
+      <c r="E13">
+        <v>-13.9349</v>
+      </c>
+      <c r="F13">
+        <v>2.4651</v>
+      </c>
+      <c r="G13">
+        <v>1.88</v>
+      </c>
+      <c r="H13">
+        <v>6.01</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.6</v>
+      </c>
+      <c r="K13">
+        <v>0.96</v>
+      </c>
+      <c r="L13">
+        <v>1.64</v>
+      </c>
+      <c r="M13">
+        <v>0.11018997</v>
+      </c>
+      <c r="N13">
+        <v>1.52981003</v>
+      </c>
+      <c r="O13">
+        <v>0.3365582066</v>
+      </c>
+      <c r="P13">
+        <v>1.1932518234</v>
+      </c>
+      <c r="Q13">
+        <v>2.1532518234</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09212397488080175</v>
+      </c>
+      <c r="T13">
+        <v>0.6454667513642466</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.034866</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.88338729922515</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08567925995707545</v>
+      </c>
+      <c r="C14">
+        <v>24.82355114323992</v>
+      </c>
+      <c r="D14">
+        <v>25.63275114323992</v>
+      </c>
+      <c r="E14">
+        <v>-13.7108</v>
+      </c>
+      <c r="F14">
+        <v>2.6892</v>
+      </c>
+      <c r="G14">
+        <v>1.88</v>
+      </c>
+      <c r="H14">
+        <v>6.01</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.6</v>
+      </c>
+      <c r="K14">
+        <v>0.96</v>
+      </c>
+      <c r="L14">
+        <v>1.64</v>
+      </c>
+      <c r="M14">
+        <v>0.12020724</v>
+      </c>
+      <c r="N14">
+        <v>1.51979276</v>
+      </c>
+      <c r="O14">
+        <v>0.3343544072</v>
+      </c>
+      <c r="P14">
+        <v>1.1854383528</v>
+      </c>
+      <c r="Q14">
+        <v>2.1454383528</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09260834086031303</v>
+      </c>
+      <c r="T14">
+        <v>0.6513298201989569</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.034866</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.64310502428972</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08564446227023736</v>
+      </c>
+      <c r="C15">
+        <v>24.61849203737882</v>
+      </c>
+      <c r="D15">
+        <v>25.65179203737882</v>
+      </c>
+      <c r="E15">
+        <v>-13.4867</v>
+      </c>
+      <c r="F15">
+        <v>2.9133</v>
+      </c>
+      <c r="G15">
+        <v>1.88</v>
+      </c>
+      <c r="H15">
+        <v>6.01</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.6</v>
+      </c>
+      <c r="K15">
+        <v>0.96</v>
+      </c>
+      <c r="L15">
+        <v>1.64</v>
+      </c>
+      <c r="M15">
+        <v>0.13342914</v>
+      </c>
+      <c r="N15">
+        <v>1.50657086</v>
+      </c>
+      <c r="O15">
+        <v>0.3314455892</v>
+      </c>
+      <c r="P15">
+        <v>1.1751252708</v>
+      </c>
+      <c r="Q15">
+        <v>2.1351252708</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09310384168992801</v>
+      </c>
+      <c r="T15">
+        <v>0.6573276722252698</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.035724</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.29116818110347</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08550670458339928</v>
+      </c>
+      <c r="C16">
+        <v>24.47004994486427</v>
+      </c>
+      <c r="D16">
+        <v>25.72744994486427</v>
+      </c>
+      <c r="E16">
+        <v>-13.2626</v>
+      </c>
+      <c r="F16">
+        <v>3.1374</v>
+      </c>
+      <c r="G16">
+        <v>1.88</v>
+      </c>
+      <c r="H16">
+        <v>6.01</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.6</v>
+      </c>
+      <c r="K16">
+        <v>0.96</v>
+      </c>
+      <c r="L16">
+        <v>1.64</v>
+      </c>
+      <c r="M16">
+        <v>0.14369292</v>
+      </c>
+      <c r="N16">
+        <v>1.49630708</v>
+      </c>
+      <c r="O16">
+        <v>0.3291875576000001</v>
+      </c>
+      <c r="P16">
+        <v>1.1671195224</v>
+      </c>
+      <c r="Q16">
+        <v>2.1271195224</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09361086579465032</v>
+      </c>
+      <c r="T16">
+        <v>0.6634650091824271</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.035724</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.41322759673894</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08536894689656119</v>
+      </c>
+      <c r="C17">
+        <v>24.32205546643682</v>
+      </c>
+      <c r="D17">
+        <v>25.80355546643682</v>
+      </c>
+      <c r="E17">
+        <v>-13.0385</v>
+      </c>
+      <c r="F17">
+        <v>3.361499999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.88</v>
+      </c>
+      <c r="H17">
+        <v>6.01</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.6</v>
+      </c>
+      <c r="K17">
+        <v>0.96</v>
+      </c>
+      <c r="L17">
+        <v>1.64</v>
+      </c>
+      <c r="M17">
+        <v>0.1539567</v>
+      </c>
+      <c r="N17">
+        <v>1.4860433</v>
+      </c>
+      <c r="O17">
+        <v>0.326929526</v>
+      </c>
+      <c r="P17">
+        <v>1.159113774</v>
+      </c>
+      <c r="Q17">
+        <v>2.119113774</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09412981987830728</v>
+      </c>
+      <c r="T17">
+        <v>0.6697467540679882</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.035724</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.65234575695634</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08523118920972308</v>
+      </c>
+      <c r="C18">
+        <v>24.17451258620386</v>
+      </c>
+      <c r="D18">
+        <v>25.88011258620386</v>
+      </c>
+      <c r="E18">
+        <v>-12.8144</v>
+      </c>
+      <c r="F18">
+        <v>3.585599999999999</v>
+      </c>
+      <c r="G18">
+        <v>1.88</v>
+      </c>
+      <c r="H18">
+        <v>6.01</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.6</v>
+      </c>
+      <c r="K18">
+        <v>0.96</v>
+      </c>
+      <c r="L18">
+        <v>1.64</v>
+      </c>
+      <c r="M18">
+        <v>0.16422048</v>
+      </c>
+      <c r="N18">
+        <v>1.47577952</v>
+      </c>
+      <c r="O18">
+        <v>0.3246714944</v>
+      </c>
+      <c r="P18">
+        <v>1.1511080256</v>
+      </c>
+      <c r="Q18">
+        <v>2.1111080256</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09466113001157511</v>
+      </c>
+      <c r="T18">
+        <v>0.6761780643079675</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.035724</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.98657414714657</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08538515152288501</v>
+      </c>
+      <c r="C19">
+        <v>23.86487970998888</v>
+      </c>
+      <c r="D19">
+        <v>25.79457970998888</v>
+      </c>
+      <c r="E19">
+        <v>-12.5903</v>
+      </c>
+      <c r="F19">
+        <v>3.8097</v>
+      </c>
+      <c r="G19">
+        <v>1.88</v>
+      </c>
+      <c r="H19">
+        <v>6.01</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.6</v>
+      </c>
+      <c r="K19">
+        <v>0.96</v>
+      </c>
+      <c r="L19">
+        <v>1.64</v>
+      </c>
+      <c r="M19">
+        <v>0.1828656</v>
+      </c>
+      <c r="N19">
+        <v>1.4571344</v>
+      </c>
+      <c r="O19">
+        <v>0.320569568</v>
+      </c>
+      <c r="P19">
+        <v>1.136564832</v>
+      </c>
+      <c r="Q19">
+        <v>2.096564832</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09520524279865664</v>
+      </c>
+      <c r="T19">
+        <v>0.6827643458790306</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.03744</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.968335214496332</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08526455383604692</v>
+      </c>
+      <c r="C20">
+        <v>23.70772895170466</v>
+      </c>
+      <c r="D20">
+        <v>25.86152895170466</v>
+      </c>
+      <c r="E20">
+        <v>-12.3662</v>
+      </c>
+      <c r="F20">
+        <v>4.033799999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.88</v>
+      </c>
+      <c r="H20">
+        <v>6.01</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.6</v>
+      </c>
+      <c r="K20">
+        <v>0.96</v>
+      </c>
+      <c r="L20">
+        <v>1.64</v>
+      </c>
+      <c r="M20">
+        <v>0.1936224</v>
+      </c>
+      <c r="N20">
+        <v>1.4463776</v>
+      </c>
+      <c r="O20">
+        <v>0.318203072</v>
+      </c>
+      <c r="P20">
+        <v>1.128174528</v>
+      </c>
+      <c r="Q20">
+        <v>2.088174528</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.0957626266293255</v>
+      </c>
+      <c r="T20">
+        <v>0.6895112684640218</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.03744</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.470094369246535</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08514395614920883</v>
+      </c>
+      <c r="C21">
+        <v>23.55092662822651</v>
+      </c>
+      <c r="D21">
+        <v>25.92882662822651</v>
+      </c>
+      <c r="E21">
+        <v>-12.1421</v>
+      </c>
+      <c r="F21">
+        <v>4.257899999999999</v>
+      </c>
+      <c r="G21">
+        <v>1.88</v>
+      </c>
+      <c r="H21">
+        <v>6.01</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.6</v>
+      </c>
+      <c r="K21">
+        <v>0.96</v>
+      </c>
+      <c r="L21">
+        <v>1.64</v>
+      </c>
+      <c r="M21">
+        <v>0.2043792</v>
+      </c>
+      <c r="N21">
+        <v>1.4356208</v>
+      </c>
+      <c r="O21">
+        <v>0.315836576</v>
+      </c>
+      <c r="P21">
+        <v>1.119784224</v>
+      </c>
+      <c r="Q21">
+        <v>2.079784224</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0963337730237146</v>
+      </c>
+      <c r="T21">
+        <v>0.6964247817301242</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.03744</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.024299928759875</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08525735846237073</v>
+      </c>
+      <c r="C22">
+        <v>23.26353441759433</v>
+      </c>
+      <c r="D22">
+        <v>25.86553441759433</v>
+      </c>
+      <c r="E22">
+        <v>-11.918</v>
+      </c>
+      <c r="F22">
+        <v>4.481999999999999</v>
+      </c>
+      <c r="G22">
+        <v>1.88</v>
+      </c>
+      <c r="H22">
+        <v>6.01</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.6</v>
+      </c>
+      <c r="K22">
+        <v>0.96</v>
+      </c>
+      <c r="L22">
+        <v>1.64</v>
+      </c>
+      <c r="M22">
+        <v>0.221859</v>
+      </c>
+      <c r="N22">
+        <v>1.418141</v>
+      </c>
+      <c r="O22">
+        <v>0.31199102</v>
+      </c>
+      <c r="P22">
+        <v>1.10614998</v>
+      </c>
+      <c r="Q22">
+        <v>2.06614998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.0969191980779634</v>
+      </c>
+      <c r="T22">
+        <v>0.703511132827879</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.392082358615157</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08514846077553265</v>
+      </c>
+      <c r="C23">
+        <v>23.10020659470175</v>
+      </c>
+      <c r="D23">
+        <v>25.92630659470175</v>
+      </c>
+      <c r="E23">
+        <v>-11.6939</v>
+      </c>
+      <c r="F23">
+        <v>4.706099999999999</v>
+      </c>
+      <c r="G23">
+        <v>1.88</v>
+      </c>
+      <c r="H23">
+        <v>6.01</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.6</v>
+      </c>
+      <c r="K23">
+        <v>0.96</v>
+      </c>
+      <c r="L23">
+        <v>1.64</v>
+      </c>
+      <c r="M23">
+        <v>0.23295195</v>
+      </c>
+      <c r="N23">
+        <v>1.40704805</v>
+      </c>
+      <c r="O23">
+        <v>0.3095505710000001</v>
+      </c>
+      <c r="P23">
+        <v>1.097497479</v>
+      </c>
+      <c r="Q23">
+        <v>2.057497479</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09751944401966156</v>
+      </c>
+      <c r="T23">
+        <v>0.7107768852192479</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.040078436776342</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08503956308869456</v>
+      </c>
+      <c r="C24">
+        <v>22.93716501800481</v>
+      </c>
+      <c r="D24">
+        <v>25.98736501800481</v>
+      </c>
+      <c r="E24">
+        <v>-11.4698</v>
+      </c>
+      <c r="F24">
+        <v>4.930199999999999</v>
+      </c>
+      <c r="G24">
+        <v>1.88</v>
+      </c>
+      <c r="H24">
+        <v>6.01</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.6</v>
+      </c>
+      <c r="K24">
+        <v>0.96</v>
+      </c>
+      <c r="L24">
+        <v>1.64</v>
+      </c>
+      <c r="M24">
+        <v>0.2440449</v>
+      </c>
+      <c r="N24">
+        <v>1.3959551</v>
+      </c>
+      <c r="O24">
+        <v>0.307110122</v>
+      </c>
+      <c r="P24">
+        <v>1.088844978</v>
+      </c>
+      <c r="Q24">
+        <v>2.048844978</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09813508088294173</v>
+      </c>
+      <c r="T24">
+        <v>0.7182289389539853</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.720074871468325</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08493066540185645</v>
+      </c>
+      <c r="C25">
+        <v>22.77441171467233</v>
+      </c>
+      <c r="D25">
+        <v>26.04871171467233</v>
+      </c>
+      <c r="E25">
+        <v>-11.2457</v>
+      </c>
+      <c r="F25">
+        <v>5.154299999999999</v>
+      </c>
+      <c r="G25">
+        <v>1.88</v>
+      </c>
+      <c r="H25">
+        <v>6.01</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.6</v>
+      </c>
+      <c r="K25">
+        <v>0.96</v>
+      </c>
+      <c r="L25">
+        <v>1.64</v>
+      </c>
+      <c r="M25">
+        <v>0.25513785</v>
+      </c>
+      <c r="N25">
+        <v>1.38486215</v>
+      </c>
+      <c r="O25">
+        <v>0.304669673</v>
+      </c>
+      <c r="P25">
+        <v>1.080192477</v>
+      </c>
+      <c r="Q25">
+        <v>2.040192477</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09876670831409928</v>
+      </c>
+      <c r="T25">
+        <v>0.7258745525259885</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.427897703143614</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08508384771501837</v>
+      </c>
+      <c r="C26">
+        <v>22.46410017193478</v>
+      </c>
+      <c r="D26">
+        <v>25.96250017193478</v>
+      </c>
+      <c r="E26">
+        <v>-11.0216</v>
+      </c>
+      <c r="F26">
+        <v>5.378399999999999</v>
+      </c>
+      <c r="G26">
+        <v>1.88</v>
+      </c>
+      <c r="H26">
+        <v>6.01</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.6</v>
+      </c>
+      <c r="K26">
+        <v>0.96</v>
+      </c>
+      <c r="L26">
+        <v>1.64</v>
+      </c>
+      <c r="M26">
+        <v>0.27376056</v>
+      </c>
+      <c r="N26">
+        <v>1.36623944</v>
+      </c>
+      <c r="O26">
+        <v>0.3005726768</v>
+      </c>
+      <c r="P26">
+        <v>1.0656667632</v>
+      </c>
+      <c r="Q26">
+        <v>2.0256667632</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09941495751976101</v>
+      </c>
+      <c r="T26">
+        <v>0.7337213664551498</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.039702</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.990636489054523</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08498587002818027</v>
+      </c>
+      <c r="C27">
+        <v>22.29507644764048</v>
+      </c>
+      <c r="D27">
+        <v>26.01757644764048</v>
+      </c>
+      <c r="E27">
+        <v>-10.7975</v>
+      </c>
+      <c r="F27">
+        <v>5.602499999999999</v>
+      </c>
+      <c r="G27">
+        <v>1.88</v>
+      </c>
+      <c r="H27">
+        <v>6.01</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.6</v>
+      </c>
+      <c r="K27">
+        <v>0.96</v>
+      </c>
+      <c r="L27">
+        <v>1.64</v>
+      </c>
+      <c r="M27">
+        <v>0.28516725</v>
+      </c>
+      <c r="N27">
+        <v>1.35483275</v>
+      </c>
+      <c r="O27">
+        <v>0.2980632050000001</v>
+      </c>
+      <c r="P27">
+        <v>1.056769545</v>
+      </c>
+      <c r="Q27">
+        <v>2.016769545</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.100080493370907</v>
+      </c>
+      <c r="T27">
+        <v>0.7417774287557553</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.039702</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.751011029492343</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08488789234134218</v>
+      </c>
+      <c r="C28">
+        <v>22.12628689530845</v>
+      </c>
+      <c r="D28">
+        <v>26.07288689530845</v>
+      </c>
+      <c r="E28">
+        <v>-10.5734</v>
+      </c>
+      <c r="F28">
+        <v>5.826599999999999</v>
+      </c>
+      <c r="G28">
+        <v>1.88</v>
+      </c>
+      <c r="H28">
+        <v>6.01</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.6</v>
+      </c>
+      <c r="K28">
+        <v>0.96</v>
+      </c>
+      <c r="L28">
+        <v>1.64</v>
+      </c>
+      <c r="M28">
+        <v>0.29657394</v>
+      </c>
+      <c r="N28">
+        <v>1.34342606</v>
+      </c>
+      <c r="O28">
+        <v>0.2955537332</v>
+      </c>
+      <c r="P28">
+        <v>1.0478723268</v>
+      </c>
+      <c r="Q28">
+        <v>2.0078723268</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1007640166774894</v>
+      </c>
+      <c r="T28">
+        <v>0.7500512224698908</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.039702</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.529818297588791</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08478991465450408</v>
+      </c>
+      <c r="C29">
+        <v>21.95773301159035</v>
+      </c>
+      <c r="D29">
+        <v>26.12843301159035</v>
+      </c>
+      <c r="E29">
+        <v>-10.3493</v>
+      </c>
+      <c r="F29">
+        <v>6.050699999999999</v>
+      </c>
+      <c r="G29">
+        <v>1.88</v>
+      </c>
+      <c r="H29">
+        <v>6.01</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.6</v>
+      </c>
+      <c r="K29">
+        <v>0.96</v>
+      </c>
+      <c r="L29">
+        <v>1.64</v>
+      </c>
+      <c r="M29">
+        <v>0.30798063</v>
+      </c>
+      <c r="N29">
+        <v>1.33201937</v>
+      </c>
+      <c r="O29">
+        <v>0.2930442614000001</v>
+      </c>
+      <c r="P29">
+        <v>1.0389751086</v>
+      </c>
+      <c r="Q29">
+        <v>1.9989751086</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1014662666500056</v>
+      </c>
+      <c r="T29">
+        <v>0.7585516954638655</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.039702</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.32501021249291</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08469193696766598</v>
+      </c>
+      <c r="C30">
+        <v>21.78941630591902</v>
+      </c>
+      <c r="D30">
+        <v>26.18421630591902</v>
+      </c>
+      <c r="E30">
+        <v>-10.1252</v>
+      </c>
+      <c r="F30">
+        <v>6.2748</v>
+      </c>
+      <c r="G30">
+        <v>1.88</v>
+      </c>
+      <c r="H30">
+        <v>6.01</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.6</v>
+      </c>
+      <c r="K30">
+        <v>0.96</v>
+      </c>
+      <c r="L30">
+        <v>1.64</v>
+      </c>
+      <c r="M30">
+        <v>0.31938732</v>
+      </c>
+      <c r="N30">
+        <v>1.32061268</v>
+      </c>
+      <c r="O30">
+        <v>0.2905347896000001</v>
+      </c>
+      <c r="P30">
+        <v>1.0300778904</v>
+      </c>
+      <c r="Q30">
+        <v>1.9900778904</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1021880235662028</v>
+      </c>
+      <c r="T30">
+        <v>0.7672882927076728</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.039702</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.134831276332449</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.0845939592808279</v>
+      </c>
+      <c r="C31">
+        <v>21.62133830064521</v>
+      </c>
+      <c r="D31">
+        <v>26.24023830064521</v>
+      </c>
+      <c r="E31">
+        <v>-9.9011</v>
+      </c>
+      <c r="F31">
+        <v>6.498899999999998</v>
+      </c>
+      <c r="G31">
+        <v>1.88</v>
+      </c>
+      <c r="H31">
+        <v>6.01</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.6</v>
+      </c>
+      <c r="K31">
+        <v>0.96</v>
+      </c>
+      <c r="L31">
+        <v>1.64</v>
+      </c>
+      <c r="M31">
+        <v>0.3307940099999999</v>
+      </c>
+      <c r="N31">
+        <v>1.30920599</v>
+      </c>
+      <c r="O31">
+        <v>0.2880253178</v>
+      </c>
+      <c r="P31">
+        <v>1.0211806722</v>
+      </c>
+      <c r="Q31">
+        <v>1.9811806722</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1029301116631379</v>
+      </c>
+      <c r="T31">
+        <v>0.7762709912822917</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.039702</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.95776812887271</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.0844959815939898</v>
+      </c>
+      <c r="C32">
+        <v>21.45350053117613</v>
+      </c>
+      <c r="D32">
+        <v>26.29650053117613</v>
+      </c>
+      <c r="E32">
+        <v>-9.677</v>
+      </c>
+      <c r="F32">
+        <v>6.722999999999999</v>
+      </c>
+      <c r="G32">
+        <v>1.88</v>
+      </c>
+      <c r="H32">
+        <v>6.01</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.6</v>
+      </c>
+      <c r="K32">
+        <v>0.96</v>
+      </c>
+      <c r="L32">
+        <v>1.64</v>
+      </c>
+      <c r="M32">
+        <v>0.3422007</v>
+      </c>
+      <c r="N32">
+        <v>1.2977993</v>
+      </c>
+      <c r="O32">
+        <v>0.285515846</v>
+      </c>
+      <c r="P32">
+        <v>1.012283454</v>
+      </c>
+      <c r="Q32">
+        <v>1.972283454</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1036934022771283</v>
+      </c>
+      <c r="T32">
+        <v>0.7855103383876139</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.039702</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.792509191243619</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08439800390715173</v>
+      </c>
+      <c r="C33">
+        <v>21.28590454611562</v>
+      </c>
+      <c r="D33">
+        <v>26.35300454611562</v>
+      </c>
+      <c r="E33">
+        <v>-9.4529</v>
+      </c>
+      <c r="F33">
+        <v>6.947099999999999</v>
+      </c>
+      <c r="G33">
+        <v>1.88</v>
+      </c>
+      <c r="H33">
+        <v>6.01</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.6</v>
+      </c>
+      <c r="K33">
+        <v>0.96</v>
+      </c>
+      <c r="L33">
+        <v>1.64</v>
+      </c>
+      <c r="M33">
+        <v>0.35360739</v>
+      </c>
+      <c r="N33">
+        <v>1.28639261</v>
+      </c>
+      <c r="O33">
+        <v>0.2830063742</v>
+      </c>
+      <c r="P33">
+        <v>1.0033862358</v>
+      </c>
+      <c r="Q33">
+        <v>1.9633862358</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1044788172567416</v>
+      </c>
+      <c r="T33">
+        <v>0.7950174926554093</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.039702</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.63791212055834</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08494898622031362</v>
+      </c>
+      <c r="C34">
+        <v>20.74717056186586</v>
+      </c>
+      <c r="D34">
+        <v>26.03837056186586</v>
+      </c>
+      <c r="E34">
+        <v>-9.2288</v>
+      </c>
+      <c r="F34">
+        <v>7.171199999999999</v>
+      </c>
+      <c r="G34">
+        <v>1.88</v>
+      </c>
+      <c r="H34">
+        <v>6.01</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.6</v>
+      </c>
+      <c r="K34">
+        <v>0.96</v>
+      </c>
+      <c r="L34">
+        <v>1.64</v>
+      </c>
+      <c r="M34">
+        <v>0.3836591999999999</v>
+      </c>
+      <c r="N34">
+        <v>1.2563408</v>
+      </c>
+      <c r="O34">
+        <v>0.2763949760000001</v>
+      </c>
+      <c r="P34">
+        <v>0.9799458240000002</v>
+      </c>
+      <c r="Q34">
+        <v>1.939945824</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1052873326769318</v>
+      </c>
+      <c r="T34">
+        <v>0.8048042691075515</v>
+      </c>
+      <c r="U34">
+        <v>0.0535</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.04173</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.274627064853393</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08487128853347553</v>
+      </c>
+      <c r="C35">
+        <v>20.56698340272813</v>
+      </c>
+      <c r="D35">
+        <v>26.08228340272813</v>
+      </c>
+      <c r="E35">
+        <v>-9.0047</v>
+      </c>
+      <c r="F35">
+        <v>7.395299999999999</v>
+      </c>
+      <c r="G35">
+        <v>1.88</v>
+      </c>
+      <c r="H35">
+        <v>6.01</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.6</v>
+      </c>
+      <c r="K35">
+        <v>0.96</v>
+      </c>
+      <c r="L35">
+        <v>1.64</v>
+      </c>
+      <c r="M35">
+        <v>0.3956485499999999</v>
+      </c>
+      <c r="N35">
+        <v>1.24435145</v>
+      </c>
+      <c r="O35">
+        <v>0.2737573190000001</v>
+      </c>
+      <c r="P35">
+        <v>0.9705941310000001</v>
+      </c>
+      <c r="Q35">
+        <v>1.930594131</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1061199828857844</v>
+      </c>
+      <c r="T35">
+        <v>0.8148831881403548</v>
+      </c>
+      <c r="U35">
+        <v>0.0535</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.04173</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.145092911372986</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08479359084663743</v>
+      </c>
+      <c r="C36">
+        <v>20.38694460887759</v>
+      </c>
+      <c r="D36">
+        <v>26.12634460887759</v>
+      </c>
+      <c r="E36">
+        <v>-8.7806</v>
+      </c>
+      <c r="F36">
+        <v>7.6194</v>
+      </c>
+      <c r="G36">
+        <v>1.88</v>
+      </c>
+      <c r="H36">
+        <v>6.01</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.6</v>
+      </c>
+      <c r="K36">
+        <v>0.96</v>
+      </c>
+      <c r="L36">
+        <v>1.64</v>
+      </c>
+      <c r="M36">
+        <v>0.4076379</v>
+      </c>
+      <c r="N36">
+        <v>1.2323621</v>
+      </c>
+      <c r="O36">
+        <v>0.271119662</v>
+      </c>
+      <c r="P36">
+        <v>0.961242438</v>
+      </c>
+      <c r="Q36">
+        <v>1.921242438</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1069778649191476</v>
+      </c>
+      <c r="T36">
+        <v>0.8252675289620308</v>
+      </c>
+      <c r="U36">
+        <v>0.0535</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.04173</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.023178413979662</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08545299315979935</v>
+      </c>
+      <c r="C37">
+        <v>19.79356986565695</v>
+      </c>
+      <c r="D37">
+        <v>25.75706986565695</v>
+      </c>
+      <c r="E37">
+        <v>-8.5565</v>
+      </c>
+      <c r="F37">
+        <v>7.8435</v>
+      </c>
+      <c r="G37">
+        <v>1.88</v>
+      </c>
+      <c r="H37">
+        <v>6.01</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.6</v>
+      </c>
+      <c r="K37">
+        <v>0.96</v>
+      </c>
+      <c r="L37">
+        <v>1.64</v>
+      </c>
+      <c r="M37">
+        <v>0.4408047</v>
+      </c>
+      <c r="N37">
+        <v>1.1991953</v>
+      </c>
+      <c r="O37">
+        <v>0.263822966</v>
+      </c>
+      <c r="P37">
+        <v>0.9353723340000002</v>
+      </c>
+      <c r="Q37">
+        <v>1.895372334</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1078621433227682</v>
+      </c>
+      <c r="T37">
+        <v>0.8359713879628354</v>
+      </c>
+      <c r="U37">
+        <v>0.0562</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.043836</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.720468497726998</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08539635547296126</v>
+      </c>
+      <c r="C38">
+        <v>19.60077748278945</v>
+      </c>
+      <c r="D38">
+        <v>25.78837748278945</v>
+      </c>
+      <c r="E38">
+        <v>-8.3324</v>
+      </c>
+      <c r="F38">
+        <v>8.067599999999999</v>
+      </c>
+      <c r="G38">
+        <v>1.88</v>
+      </c>
+      <c r="H38">
+        <v>6.01</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.6</v>
+      </c>
+      <c r="K38">
+        <v>0.96</v>
+      </c>
+      <c r="L38">
+        <v>1.64</v>
+      </c>
+      <c r="M38">
+        <v>0.4533991199999999</v>
+      </c>
+      <c r="N38">
+        <v>1.18660088</v>
+      </c>
+      <c r="O38">
+        <v>0.2610521936000001</v>
+      </c>
+      <c r="P38">
+        <v>0.9255486864000002</v>
+      </c>
+      <c r="Q38">
+        <v>1.8855486864</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.108774055426502</v>
+      </c>
+      <c r="T38">
+        <v>0.847009742557415</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.043836</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.617122150567916</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08533971778612316</v>
+      </c>
+      <c r="C39">
+        <v>19.40806130111524</v>
+      </c>
+      <c r="D39">
+        <v>25.81976130111524</v>
+      </c>
+      <c r="E39">
+        <v>-8.1083</v>
+      </c>
+      <c r="F39">
+        <v>8.291699999999999</v>
+      </c>
+      <c r="G39">
+        <v>1.88</v>
+      </c>
+      <c r="H39">
+        <v>6.01</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.6</v>
+      </c>
+      <c r="K39">
+        <v>0.96</v>
+      </c>
+      <c r="L39">
+        <v>1.64</v>
+      </c>
+      <c r="M39">
+        <v>0.4659935399999999</v>
+      </c>
+      <c r="N39">
+        <v>1.17400646</v>
+      </c>
+      <c r="O39">
+        <v>0.2582814212</v>
+      </c>
+      <c r="P39">
+        <v>0.9157250388000002</v>
+      </c>
+      <c r="Q39">
+        <v>1.8757250388</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1097149171208304</v>
+      </c>
+      <c r="T39">
+        <v>0.8583985211073782</v>
+      </c>
+      <c r="U39">
+        <v>0.0562</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.043836</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.519362092444458</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08667616009928508</v>
+      </c>
+      <c r="C40">
+        <v>18.46321382581664</v>
+      </c>
+      <c r="D40">
+        <v>25.09901382581664</v>
+      </c>
+      <c r="E40">
+        <v>-7.8842</v>
+      </c>
+      <c r="F40">
+        <v>8.515799999999999</v>
+      </c>
+      <c r="G40">
+        <v>1.88</v>
+      </c>
+      <c r="H40">
+        <v>6.01</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.6</v>
+      </c>
+      <c r="K40">
+        <v>0.96</v>
+      </c>
+      <c r="L40">
+        <v>1.64</v>
+      </c>
+      <c r="M40">
+        <v>0.51861222</v>
+      </c>
+      <c r="N40">
+        <v>1.12138778</v>
+      </c>
+      <c r="O40">
+        <v>0.2467053116</v>
+      </c>
+      <c r="P40">
+        <v>0.8746824684000001</v>
+      </c>
+      <c r="Q40">
+        <v>1.8346824684</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1106861291923953</v>
+      </c>
+      <c r="T40">
+        <v>0.870154679610566</v>
+      </c>
+      <c r="U40">
+        <v>0.0609</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.047502</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.162285686210788</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08665618241244699</v>
+      </c>
+      <c r="C41">
+        <v>18.24959147390474</v>
+      </c>
+      <c r="D41">
+        <v>25.10949147390474</v>
+      </c>
+      <c r="E41">
+        <v>-7.6601</v>
+      </c>
+      <c r="F41">
+        <v>8.739899999999999</v>
+      </c>
+      <c r="G41">
+        <v>1.88</v>
+      </c>
+      <c r="H41">
+        <v>6.01</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.6</v>
+      </c>
+      <c r="K41">
+        <v>0.96</v>
+      </c>
+      <c r="L41">
+        <v>1.64</v>
+      </c>
+      <c r="M41">
+        <v>0.5322599099999999</v>
+      </c>
+      <c r="N41">
+        <v>1.10774009</v>
+      </c>
+      <c r="O41">
+        <v>0.2437028198</v>
+      </c>
+      <c r="P41">
+        <v>0.8640372702000001</v>
+      </c>
+      <c r="Q41">
+        <v>1.8240372702</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1116891842827</v>
+      </c>
+      <c r="T41">
+        <v>0.8822962859335305</v>
+      </c>
+      <c r="U41">
+        <v>0.0609</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.047502</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.081201437846409</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08663620472560889</v>
+      </c>
+      <c r="C42">
+        <v>18.03597787348863</v>
+      </c>
+      <c r="D42">
+        <v>25.11997787348863</v>
+      </c>
+      <c r="E42">
+        <v>-7.436</v>
+      </c>
+      <c r="F42">
+        <v>8.963999999999999</v>
+      </c>
+      <c r="G42">
+        <v>1.88</v>
+      </c>
+      <c r="H42">
+        <v>6.01</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.6</v>
+      </c>
+      <c r="K42">
+        <v>0.96</v>
+      </c>
+      <c r="L42">
+        <v>1.64</v>
+      </c>
+      <c r="M42">
+        <v>0.5459075999999999</v>
+      </c>
+      <c r="N42">
+        <v>1.0940924</v>
+      </c>
+      <c r="O42">
+        <v>0.240700328</v>
+      </c>
+      <c r="P42">
+        <v>0.8533920720000001</v>
+      </c>
+      <c r="Q42">
+        <v>1.813392072</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1127256745426815</v>
+      </c>
+      <c r="T42">
+        <v>0.8948426124672604</v>
+      </c>
+      <c r="U42">
+        <v>0.0609</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.047502</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.004171401900249</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08959036703877081</v>
+      </c>
+      <c r="C43">
+        <v>16.3508037315224</v>
+      </c>
+      <c r="D43">
+        <v>23.6589037315224</v>
+      </c>
+      <c r="E43">
+        <v>-7.2119</v>
+      </c>
+      <c r="F43">
+        <v>9.188099999999999</v>
+      </c>
+      <c r="G43">
+        <v>1.88</v>
+      </c>
+      <c r="H43">
+        <v>6.01</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.6</v>
+      </c>
+      <c r="K43">
+        <v>0.96</v>
+      </c>
+      <c r="L43">
+        <v>1.64</v>
+      </c>
+      <c r="M43">
+        <v>0.6450046199999999</v>
+      </c>
+      <c r="N43">
+        <v>0.9949953800000002</v>
+      </c>
+      <c r="O43">
+        <v>0.2188989836</v>
+      </c>
+      <c r="P43">
+        <v>0.7760963964000002</v>
+      </c>
+      <c r="Q43">
+        <v>1.7360963964</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1137973000657132</v>
+      </c>
+      <c r="T43">
+        <v>0.9078142382055235</v>
+      </c>
+      <c r="U43">
+        <v>0.0702</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.054756</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.542617446678134</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09118264935193272</v>
+      </c>
+      <c r="C44">
+        <v>15.40754090897392</v>
+      </c>
+      <c r="D44">
+        <v>22.93974090897392</v>
+      </c>
+      <c r="E44">
+        <v>-6.9878</v>
+      </c>
+      <c r="F44">
+        <v>9.412199999999999</v>
+      </c>
+      <c r="G44">
+        <v>1.88</v>
+      </c>
+      <c r="H44">
+        <v>6.01</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.6</v>
+      </c>
+      <c r="K44">
+        <v>0.96</v>
+      </c>
+      <c r="L44">
+        <v>1.64</v>
+      </c>
+      <c r="M44">
+        <v>0.7049737799999999</v>
+      </c>
+      <c r="N44">
+        <v>0.9350262200000002</v>
+      </c>
+      <c r="O44">
+        <v>0.2057057684</v>
+      </c>
+      <c r="P44">
+        <v>0.7293204516000003</v>
+      </c>
+      <c r="Q44">
+        <v>1.6893204516</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1149058781929874</v>
+      </c>
+      <c r="T44">
+        <v>0.9212331613830371</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.326327654341982</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09127187166509462</v>
+      </c>
+      <c r="C45">
+        <v>15.14443454837949</v>
+      </c>
+      <c r="D45">
+        <v>22.90073454837949</v>
+      </c>
+      <c r="E45">
+        <v>-6.7637</v>
+      </c>
+      <c r="F45">
+        <v>9.636299999999999</v>
+      </c>
+      <c r="G45">
+        <v>1.88</v>
+      </c>
+      <c r="H45">
+        <v>6.01</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.6</v>
+      </c>
+      <c r="K45">
+        <v>0.96</v>
+      </c>
+      <c r="L45">
+        <v>1.64</v>
+      </c>
+      <c r="M45">
+        <v>0.7217588699999998</v>
+      </c>
+      <c r="N45">
+        <v>0.9182411300000003</v>
+      </c>
+      <c r="O45">
+        <v>0.2020130486000001</v>
+      </c>
+      <c r="P45">
+        <v>0.7162280814000002</v>
+      </c>
+      <c r="Q45">
+        <v>1.6762280814</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1160533537984116</v>
+      </c>
+      <c r="T45">
+        <v>0.9351229239702881</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.27222701121775</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09136109397825652</v>
+      </c>
+      <c r="C46">
+        <v>14.88146061416575</v>
+      </c>
+      <c r="D46">
+        <v>22.86186061416575</v>
+      </c>
+      <c r="E46">
+        <v>-6.5396</v>
+      </c>
+      <c r="F46">
+        <v>9.860399999999998</v>
+      </c>
+      <c r="G46">
+        <v>1.88</v>
+      </c>
+      <c r="H46">
+        <v>6.01</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.6</v>
+      </c>
+      <c r="K46">
+        <v>0.96</v>
+      </c>
+      <c r="L46">
+        <v>1.64</v>
+      </c>
+      <c r="M46">
+        <v>0.7385439599999998</v>
+      </c>
+      <c r="N46">
+        <v>0.9014560400000003</v>
+      </c>
+      <c r="O46">
+        <v>0.1983203288000001</v>
+      </c>
+      <c r="P46">
+        <v>0.7031357112000003</v>
+      </c>
+      <c r="Q46">
+        <v>1.6631357112</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1172418106754581</v>
+      </c>
+      <c r="T46">
+        <v>0.9495087495070836</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.220585488235528</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09145031629141845</v>
+      </c>
+      <c r="C47">
+        <v>14.61861843309525</v>
+      </c>
+      <c r="D47">
+        <v>22.82311843309525</v>
+      </c>
+      <c r="E47">
+        <v>-6.3155</v>
+      </c>
+      <c r="F47">
+        <v>10.0845</v>
+      </c>
+      <c r="G47">
+        <v>1.88</v>
+      </c>
+      <c r="H47">
+        <v>6.01</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.6</v>
+      </c>
+      <c r="K47">
+        <v>0.96</v>
+      </c>
+      <c r="L47">
+        <v>1.64</v>
+      </c>
+      <c r="M47">
+        <v>0.7553290499999998</v>
+      </c>
+      <c r="N47">
+        <v>0.8846709500000003</v>
+      </c>
+      <c r="O47">
+        <v>0.1946276090000001</v>
+      </c>
+      <c r="P47">
+        <v>0.6900433410000002</v>
+      </c>
+      <c r="Q47">
+        <v>1.650043341</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1184734841662153</v>
+      </c>
+      <c r="T47">
+        <v>0.9644176959724899</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.171239144052517</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09153953860458035</v>
+      </c>
+      <c r="C48">
+        <v>14.35590733648637</v>
+      </c>
+      <c r="D48">
+        <v>22.78450733648637</v>
+      </c>
+      <c r="E48">
+        <v>-6.0914</v>
+      </c>
+      <c r="F48">
+        <v>10.3086</v>
+      </c>
+      <c r="G48">
+        <v>1.88</v>
+      </c>
+      <c r="H48">
+        <v>6.01</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.6</v>
+      </c>
+      <c r="K48">
+        <v>0.96</v>
+      </c>
+      <c r="L48">
+        <v>1.64</v>
+      </c>
+      <c r="M48">
+        <v>0.7721141399999998</v>
+      </c>
+      <c r="N48">
+        <v>0.8678858600000003</v>
+      </c>
+      <c r="O48">
+        <v>0.1909348892000001</v>
+      </c>
+      <c r="P48">
+        <v>0.6769509708000003</v>
+      </c>
+      <c r="Q48">
+        <v>1.6369509708</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1197507751936673</v>
+      </c>
+      <c r="T48">
+        <v>0.9798788256403187</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.124038293094853</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09162876091774226</v>
+      </c>
+      <c r="C49">
+        <v>14.09332666017483</v>
+      </c>
+      <c r="D49">
+        <v>22.74602666017483</v>
+      </c>
+      <c r="E49">
+        <v>-5.8673</v>
+      </c>
+      <c r="F49">
+        <v>10.5327</v>
+      </c>
+      <c r="G49">
+        <v>1.88</v>
+      </c>
+      <c r="H49">
+        <v>6.01</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.6</v>
+      </c>
+      <c r="K49">
+        <v>0.96</v>
+      </c>
+      <c r="L49">
+        <v>1.64</v>
+      </c>
+      <c r="M49">
+        <v>0.7888992299999998</v>
+      </c>
+      <c r="N49">
+        <v>0.8511007700000003</v>
+      </c>
+      <c r="O49">
+        <v>0.1872421694000001</v>
+      </c>
+      <c r="P49">
+        <v>0.6638586006000002</v>
+      </c>
+      <c r="Q49">
+        <v>1.6238586006</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1210762658825326</v>
+      </c>
+      <c r="T49">
+        <v>0.9959233941635374</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.078845988986452</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09171798323090416</v>
+      </c>
+      <c r="C50">
+        <v>13.83087574447557</v>
+      </c>
+      <c r="D50">
+        <v>22.70767574447557</v>
+      </c>
+      <c r="E50">
+        <v>-5.6432</v>
+      </c>
+      <c r="F50">
+        <v>10.7568</v>
+      </c>
+      <c r="G50">
+        <v>1.88</v>
+      </c>
+      <c r="H50">
+        <v>6.01</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.6</v>
+      </c>
+      <c r="K50">
+        <v>0.96</v>
+      </c>
+      <c r="L50">
+        <v>1.64</v>
+      </c>
+      <c r="M50">
+        <v>0.8056843199999998</v>
+      </c>
+      <c r="N50">
+        <v>0.8343156800000003</v>
+      </c>
+      <c r="O50">
+        <v>0.1835494496000001</v>
+      </c>
+      <c r="P50">
+        <v>0.6507662304000003</v>
+      </c>
+      <c r="Q50">
+        <v>1.6107662304</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.122452736982508</v>
+      </c>
+      <c r="T50">
+        <v>1.01258506147611</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.035536697549234</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09803706554406608</v>
+      </c>
+      <c r="C51">
+        <v>11.18444656844323</v>
+      </c>
+      <c r="D51">
+        <v>20.28534656844323</v>
+      </c>
+      <c r="E51">
+        <v>-5.4191</v>
+      </c>
+      <c r="F51">
+        <v>10.9809</v>
+      </c>
+      <c r="G51">
+        <v>1.88</v>
+      </c>
+      <c r="H51">
+        <v>6.01</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.6</v>
+      </c>
+      <c r="K51">
+        <v>0.96</v>
+      </c>
+      <c r="L51">
+        <v>1.64</v>
+      </c>
+      <c r="M51">
+        <v>1.00145808</v>
+      </c>
+      <c r="N51">
+        <v>0.6385419200000002</v>
+      </c>
+      <c r="O51">
+        <v>0.1404792224</v>
+      </c>
+      <c r="P51">
+        <v>0.4980626976000002</v>
+      </c>
+      <c r="Q51">
+        <v>1.4580626976</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.123883187341306</v>
+      </c>
+      <c r="T51">
+        <v>1.029900127506824</v>
+      </c>
+      <c r="U51">
+        <v>0.0912</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.071136</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.637612230359158</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09825342785722797</v>
+      </c>
+      <c r="C52">
+        <v>10.88652434044018</v>
+      </c>
+      <c r="D52">
+        <v>20.21152434044018</v>
+      </c>
+      <c r="E52">
+        <v>-5.195</v>
+      </c>
+      <c r="F52">
+        <v>11.205</v>
+      </c>
+      <c r="G52">
+        <v>1.88</v>
+      </c>
+      <c r="H52">
+        <v>6.01</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.6</v>
+      </c>
+      <c r="K52">
+        <v>0.96</v>
+      </c>
+      <c r="L52">
+        <v>1.64</v>
+      </c>
+      <c r="M52">
+        <v>1.021896</v>
+      </c>
+      <c r="N52">
+        <v>0.6181040000000002</v>
+      </c>
+      <c r="O52">
+        <v>0.1359828800000001</v>
+      </c>
+      <c r="P52">
+        <v>0.4821211200000002</v>
+      </c>
+      <c r="Q52">
+        <v>1.44212112</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1253708557144559</v>
+      </c>
+      <c r="T52">
+        <v>1.047907796178766</v>
+      </c>
+      <c r="U52">
+        <v>0.0912</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.071136</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.604859985751975</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.0984697901703899</v>
+      </c>
+      <c r="C53">
+        <v>10.58913747037848</v>
+      </c>
+      <c r="D53">
+        <v>20.13823747037848</v>
+      </c>
+      <c r="E53">
+        <v>-4.9709</v>
+      </c>
+      <c r="F53">
+        <v>11.4291</v>
+      </c>
+      <c r="G53">
+        <v>1.88</v>
+      </c>
+      <c r="H53">
+        <v>6.01</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.6</v>
+      </c>
+      <c r="K53">
+        <v>0.96</v>
+      </c>
+      <c r="L53">
+        <v>1.64</v>
+      </c>
+      <c r="M53">
+        <v>1.04233392</v>
+      </c>
+      <c r="N53">
+        <v>0.5976660800000002</v>
+      </c>
+      <c r="O53">
+        <v>0.1314865376</v>
+      </c>
+      <c r="P53">
+        <v>0.4661795424000001</v>
+      </c>
+      <c r="Q53">
+        <v>1.4261795424</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1269192452456936</v>
+      </c>
+      <c r="T53">
+        <v>1.066650471735276</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.071136</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.573392142894093</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.0986861524835518</v>
+      </c>
+      <c r="C54">
+        <v>10.29228015568388</v>
+      </c>
+      <c r="D54">
+        <v>20.06548015568388</v>
+      </c>
+      <c r="E54">
+        <v>-4.7468</v>
+      </c>
+      <c r="F54">
+        <v>11.6532</v>
+      </c>
+      <c r="G54">
+        <v>1.88</v>
+      </c>
+      <c r="H54">
+        <v>6.01</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.6</v>
+      </c>
+      <c r="K54">
+        <v>0.96</v>
+      </c>
+      <c r="L54">
+        <v>1.64</v>
+      </c>
+      <c r="M54">
+        <v>1.06277184</v>
+      </c>
+      <c r="N54">
+        <v>0.5772281600000002</v>
+      </c>
+      <c r="O54">
+        <v>0.1269901952</v>
+      </c>
+      <c r="P54">
+        <v>0.4502379648000002</v>
+      </c>
+      <c r="Q54">
+        <v>1.4102379648</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1285321510073996</v>
+      </c>
+      <c r="T54">
+        <v>1.086174092106642</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.071136</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.543134601684591</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09890251479671371</v>
+      </c>
+      <c r="C55">
+        <v>9.995946677336555</v>
+      </c>
+      <c r="D55">
+        <v>19.99324667733655</v>
+      </c>
+      <c r="E55">
+        <v>-4.5227</v>
+      </c>
+      <c r="F55">
+        <v>11.8773</v>
+      </c>
+      <c r="G55">
+        <v>1.88</v>
+      </c>
+      <c r="H55">
+        <v>6.01</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.6</v>
+      </c>
+      <c r="K55">
+        <v>0.96</v>
+      </c>
+      <c r="L55">
+        <v>1.64</v>
+      </c>
+      <c r="M55">
+        <v>1.08320976</v>
+      </c>
+      <c r="N55">
+        <v>0.5567902400000002</v>
+      </c>
+      <c r="O55">
+        <v>0.1224938528000001</v>
+      </c>
+      <c r="P55">
+        <v>0.4342963872000002</v>
+      </c>
+      <c r="Q55">
+        <v>1.3942963872</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1302136910568377</v>
+      </c>
+      <c r="T55">
+        <v>1.106528504834235</v>
+      </c>
+      <c r="U55">
+        <v>0.0912</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.071136</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.514018854482995</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1299471885196703</v>
+      </c>
+      <c r="C56">
+        <v>2.962159732066155</v>
+      </c>
+      <c r="D56">
+        <v>13.18355973206615</v>
+      </c>
+      <c r="E56">
+        <v>-4.2986</v>
+      </c>
+      <c r="F56">
+        <v>12.1014</v>
+      </c>
+      <c r="G56">
+        <v>1.88</v>
+      </c>
+      <c r="H56">
+        <v>6.01</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.6</v>
+      </c>
+      <c r="K56">
+        <v>0.96</v>
+      </c>
+      <c r="L56">
+        <v>1.64</v>
+      </c>
+      <c r="M56">
+        <v>1.89507924</v>
+      </c>
+      <c r="N56">
+        <v>-0.2550792399999997</v>
+      </c>
+      <c r="O56">
+        <v>-0.05611743279999994</v>
+      </c>
+      <c r="P56">
+        <v>-0.1989618071999998</v>
+      </c>
+      <c r="Q56">
+        <v>0.7610381928000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1336590084711611</v>
+      </c>
+      <c r="T56">
+        <v>1.14823278220315</v>
+      </c>
+      <c r="U56">
+        <v>0.1566</v>
+      </c>
+      <c r="V56">
+        <v>0.1903878172397689</v>
+      </c>
+      <c r="W56">
+        <v>0.1267852678202522</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8653991692716766</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1311251885196703</v>
+      </c>
+      <c r="C57">
+        <v>2.569847420633229</v>
+      </c>
+      <c r="D57">
+        <v>13.01534742063323</v>
+      </c>
+      <c r="E57">
+        <v>-4.074499999999999</v>
+      </c>
+      <c r="F57">
+        <v>12.3255</v>
+      </c>
+      <c r="G57">
+        <v>1.88</v>
+      </c>
+      <c r="H57">
+        <v>6.01</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.6</v>
+      </c>
+      <c r="K57">
+        <v>0.96</v>
+      </c>
+      <c r="L57">
+        <v>1.64</v>
+      </c>
+      <c r="M57">
+        <v>1.9301733</v>
+      </c>
+      <c r="N57">
+        <v>-0.2901733</v>
+      </c>
+      <c r="O57">
+        <v>-0.063838126</v>
+      </c>
+      <c r="P57">
+        <v>-0.226335174</v>
+      </c>
+      <c r="Q57">
+        <v>0.733664826</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1357669864371869</v>
+      </c>
+      <c r="T57">
+        <v>1.173749066252109</v>
+      </c>
+      <c r="U57">
+        <v>0.1566</v>
+      </c>
+      <c r="V57">
+        <v>0.1869262205626821</v>
+      </c>
+      <c r="W57">
+        <v>0.127327353859884</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.8496646389212824</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1323031885196703</v>
+      </c>
+      <c r="C58">
+        <v>2.181773555097292</v>
+      </c>
+      <c r="D58">
+        <v>12.85137355509729</v>
+      </c>
+      <c r="E58">
+        <v>-3.850399999999999</v>
+      </c>
+      <c r="F58">
+        <v>12.5496</v>
+      </c>
+      <c r="G58">
+        <v>1.88</v>
+      </c>
+      <c r="H58">
+        <v>6.01</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.6</v>
+      </c>
+      <c r="K58">
+        <v>0.96</v>
+      </c>
+      <c r="L58">
+        <v>1.64</v>
+      </c>
+      <c r="M58">
+        <v>1.96526736</v>
+      </c>
+      <c r="N58">
+        <v>-0.32526736</v>
+      </c>
+      <c r="O58">
+        <v>-0.0715588192</v>
+      </c>
+      <c r="P58">
+        <v>-0.2537085408</v>
+      </c>
+      <c r="Q58">
+        <v>0.7062914592</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1379707815834866</v>
+      </c>
+      <c r="T58">
+        <v>1.200425181394202</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.1835882523383485</v>
+      </c>
+      <c r="W58">
+        <v>0.1278500796838146</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8344920560834024</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1334811885196703</v>
+      </c>
+      <c r="C59">
+        <v>1.797779934362277</v>
+      </c>
+      <c r="D59">
+        <v>12.69147993436228</v>
+      </c>
+      <c r="E59">
+        <v>-3.626299999999999</v>
+      </c>
+      <c r="F59">
+        <v>12.7737</v>
+      </c>
+      <c r="G59">
+        <v>1.88</v>
+      </c>
+      <c r="H59">
+        <v>6.01</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.6</v>
+      </c>
+      <c r="K59">
+        <v>0.96</v>
+      </c>
+      <c r="L59">
+        <v>1.64</v>
+      </c>
+      <c r="M59">
+        <v>2.00036142</v>
+      </c>
+      <c r="N59">
+        <v>-0.3603614200000003</v>
+      </c>
+      <c r="O59">
+        <v>-0.07927951240000006</v>
+      </c>
+      <c r="P59">
+        <v>-0.2810819076000002</v>
+      </c>
+      <c r="Q59">
+        <v>0.6789180923999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1402770788296142</v>
+      </c>
+      <c r="T59">
+        <v>1.228342046077789</v>
+      </c>
+      <c r="U59">
+        <v>0.1566</v>
+      </c>
+      <c r="V59">
+        <v>0.1803674058060968</v>
+      </c>
+      <c r="W59">
+        <v>0.1283544642507653</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8198518445731671</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1346591885196703</v>
+      </c>
+      <c r="C60">
+        <v>1.41771613377564</v>
+      </c>
+      <c r="D60">
+        <v>12.53551613377564</v>
+      </c>
+      <c r="E60">
+        <v>-3.402200000000002</v>
+      </c>
+      <c r="F60">
+        <v>12.9978</v>
+      </c>
+      <c r="G60">
+        <v>1.88</v>
+      </c>
+      <c r="H60">
+        <v>6.01</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.6</v>
+      </c>
+      <c r="K60">
+        <v>0.96</v>
+      </c>
+      <c r="L60">
+        <v>1.64</v>
+      </c>
+      <c r="M60">
+        <v>2.03545548</v>
+      </c>
+      <c r="N60">
+        <v>-0.3954554799999994</v>
+      </c>
+      <c r="O60">
+        <v>-0.08700020559999987</v>
+      </c>
+      <c r="P60">
+        <v>-0.3084552743999995</v>
+      </c>
+      <c r="Q60">
+        <v>0.6515447256000004</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1426931997541288</v>
+      </c>
+      <c r="T60">
+        <v>1.257588285270116</v>
+      </c>
+      <c r="U60">
+        <v>0.1566</v>
+      </c>
+      <c r="V60">
+        <v>0.177257622947371</v>
+      </c>
+      <c r="W60">
+        <v>0.1288414562464417</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.8057164679425955</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1678852305952699</v>
+      </c>
+      <c r="C61">
+        <v>-2.032977525154148</v>
+      </c>
+      <c r="D61">
+        <v>9.308922474845851</v>
+      </c>
+      <c r="E61">
+        <v>-3.178100000000001</v>
+      </c>
+      <c r="F61">
+        <v>13.2219</v>
+      </c>
+      <c r="G61">
+        <v>1.88</v>
+      </c>
+      <c r="H61">
+        <v>6.01</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.6</v>
+      </c>
+      <c r="K61">
+        <v>0.96</v>
+      </c>
+      <c r="L61">
+        <v>1.64</v>
+      </c>
+      <c r="M61">
+        <v>2.76073272</v>
+      </c>
+      <c r="N61">
+        <v>-1.120732719999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.2465611983999999</v>
+      </c>
+      <c r="P61">
+        <v>-0.8741715215999996</v>
+      </c>
+      <c r="Q61">
+        <v>0.08582847840000041</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1482760633471554</v>
+      </c>
+      <c r="T61">
+        <v>1.325166758832071</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.1306899423425532</v>
+      </c>
+      <c r="W61">
+        <v>0.1815119400388749</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.594045192466151</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1695852305952699</v>
+      </c>
+      <c r="C62">
+        <v>-2.378078712636935</v>
+      </c>
+      <c r="D62">
+        <v>9.187921287363062</v>
+      </c>
+      <c r="E62">
+        <v>-2.954000000000001</v>
+      </c>
+      <c r="F62">
+        <v>13.446</v>
+      </c>
+      <c r="G62">
+        <v>1.88</v>
+      </c>
+      <c r="H62">
+        <v>6.01</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.6</v>
+      </c>
+      <c r="K62">
+        <v>0.96</v>
+      </c>
+      <c r="L62">
+        <v>1.64</v>
+      </c>
+      <c r="M62">
+        <v>2.8075248</v>
+      </c>
+      <c r="N62">
+        <v>-1.1675248</v>
+      </c>
+      <c r="O62">
+        <v>-0.256855456</v>
+      </c>
+      <c r="P62">
+        <v>-0.9106693439999998</v>
+      </c>
+      <c r="Q62">
+        <v>0.04933065600000019</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1510129649308343</v>
+      </c>
+      <c r="T62">
+        <v>1.358295927802873</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.128511776636844</v>
+      </c>
+      <c r="W62">
+        <v>0.181966741038227</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5841444392583817</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1712852305952699</v>
+      </c>
+      <c r="C63">
+        <v>-2.720074617850951</v>
+      </c>
+      <c r="D63">
+        <v>9.070025382149046</v>
+      </c>
+      <c r="E63">
+        <v>-2.729900000000001</v>
+      </c>
+      <c r="F63">
+        <v>13.6701</v>
+      </c>
+      <c r="G63">
+        <v>1.88</v>
+      </c>
+      <c r="H63">
+        <v>6.01</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.6</v>
+      </c>
+      <c r="K63">
+        <v>0.96</v>
+      </c>
+      <c r="L63">
+        <v>1.64</v>
+      </c>
+      <c r="M63">
+        <v>2.85431688</v>
+      </c>
+      <c r="N63">
+        <v>-1.21431688</v>
+      </c>
+      <c r="O63">
+        <v>-0.2671497135999999</v>
+      </c>
+      <c r="P63">
+        <v>-0.9471671663999998</v>
+      </c>
+      <c r="Q63">
+        <v>0.0128328336000002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1538902204418813</v>
+      </c>
+      <c r="T63">
+        <v>1.393124028515767</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.1264050262001744</v>
+      </c>
+      <c r="W63">
+        <v>0.1824066305294036</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5745683009098836</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1729852305952699</v>
+      </c>
+      <c r="C64">
+        <v>-3.059083263767135</v>
+      </c>
+      <c r="D64">
+        <v>8.955116736232863</v>
+      </c>
+      <c r="E64">
+        <v>-2.505800000000001</v>
+      </c>
+      <c r="F64">
+        <v>13.8942</v>
+      </c>
+      <c r="G64">
+        <v>1.88</v>
+      </c>
+      <c r="H64">
+        <v>6.01</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.6</v>
+      </c>
+      <c r="K64">
+        <v>0.96</v>
+      </c>
+      <c r="L64">
+        <v>1.64</v>
+      </c>
+      <c r="M64">
+        <v>2.90110896</v>
+      </c>
+      <c r="N64">
+        <v>-1.26110896</v>
+      </c>
+      <c r="O64">
+        <v>-0.2774439711999999</v>
+      </c>
+      <c r="P64">
+        <v>-0.9836649887999998</v>
+      </c>
+      <c r="Q64">
+        <v>-0.02366498879999979</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1569189104535097</v>
+      </c>
+      <c r="T64">
+        <v>1.429785187160919</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1243662354550103</v>
+      </c>
+      <c r="W64">
+        <v>0.1828323300369938</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5653010702500468</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1746852305952699</v>
+      </c>
+      <c r="C65">
+        <v>-3.395216767223733</v>
+      </c>
+      <c r="D65">
+        <v>8.843083232776264</v>
+      </c>
+      <c r="E65">
+        <v>-2.281700000000001</v>
+      </c>
+      <c r="F65">
+        <v>14.1183</v>
+      </c>
+      <c r="G65">
+        <v>1.88</v>
+      </c>
+      <c r="H65">
+        <v>6.01</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.6</v>
+      </c>
+      <c r="K65">
+        <v>0.96</v>
+      </c>
+      <c r="L65">
+        <v>1.64</v>
+      </c>
+      <c r="M65">
+        <v>2.94790104</v>
+      </c>
+      <c r="N65">
+        <v>-1.30790104</v>
+      </c>
+      <c r="O65">
+        <v>-0.2877382287999999</v>
+      </c>
+      <c r="P65">
+        <v>-1.0201628112</v>
+      </c>
+      <c r="Q65">
+        <v>-0.06016281119999967</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1601113134387397</v>
+      </c>
+      <c r="T65">
+        <v>1.46842803005716</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.1223921682255657</v>
+      </c>
+      <c r="W65">
+        <v>0.1832445152745019</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.556328037388935</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1763852305952699</v>
+      </c>
+      <c r="C66">
+        <v>-3.728581703806515</v>
+      </c>
+      <c r="D66">
+        <v>8.733818296193482</v>
+      </c>
+      <c r="E66">
+        <v>-2.057600000000001</v>
+      </c>
+      <c r="F66">
+        <v>14.3424</v>
+      </c>
+      <c r="G66">
+        <v>1.88</v>
+      </c>
+      <c r="H66">
+        <v>6.01</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.6</v>
+      </c>
+      <c r="K66">
+        <v>0.96</v>
+      </c>
+      <c r="L66">
+        <v>1.64</v>
+      </c>
+      <c r="M66">
+        <v>2.99469312</v>
+      </c>
+      <c r="N66">
+        <v>-1.354693119999999</v>
+      </c>
+      <c r="O66">
+        <v>-0.2980324863999999</v>
+      </c>
+      <c r="P66">
+        <v>-1.0566606336</v>
+      </c>
+      <c r="Q66">
+        <v>-0.09666063359999955</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1634810721453714</v>
+      </c>
+      <c r="T66">
+        <v>1.509217697558748</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1204797905970412</v>
+      </c>
+      <c r="W66">
+        <v>0.1836438197233378</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5476354118047329</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1780852305952699</v>
+      </c>
+      <c r="C67">
+        <v>-4.059279446008436</v>
+      </c>
+      <c r="D67">
+        <v>8.627220553991563</v>
+      </c>
+      <c r="E67">
+        <v>-1.833500000000001</v>
+      </c>
+      <c r="F67">
+        <v>14.5665</v>
+      </c>
+      <c r="G67">
+        <v>1.88</v>
+      </c>
+      <c r="H67">
+        <v>6.01</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.6</v>
+      </c>
+      <c r="K67">
+        <v>0.96</v>
+      </c>
+      <c r="L67">
+        <v>1.64</v>
+      </c>
+      <c r="M67">
+        <v>3.0414852</v>
+      </c>
+      <c r="N67">
+        <v>-1.4014852</v>
+      </c>
+      <c r="O67">
+        <v>-0.3083267439999999</v>
+      </c>
+      <c r="P67">
+        <v>-1.093158456</v>
+      </c>
+      <c r="Q67">
+        <v>-0.1331584559999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.167043388492382</v>
+      </c>
+      <c r="T67">
+        <v>1.552338203203284</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1186262553570867</v>
+      </c>
+      <c r="W67">
+        <v>0.1840308378814403</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5392102516231215</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1797852305952699</v>
+      </c>
+      <c r="C68">
+        <v>-4.387406476924092</v>
+      </c>
+      <c r="D68">
+        <v>8.523193523075907</v>
+      </c>
+      <c r="E68">
+        <v>-1.609400000000001</v>
+      </c>
+      <c r="F68">
+        <v>14.7906</v>
+      </c>
+      <c r="G68">
+        <v>1.88</v>
+      </c>
+      <c r="H68">
+        <v>6.01</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.6</v>
+      </c>
+      <c r="K68">
+        <v>0.96</v>
+      </c>
+      <c r="L68">
+        <v>1.64</v>
+      </c>
+      <c r="M68">
+        <v>3.08827728</v>
+      </c>
+      <c r="N68">
+        <v>-1.44827728</v>
+      </c>
+      <c r="O68">
+        <v>-0.3186210016</v>
+      </c>
+      <c r="P68">
+        <v>-1.1296562784</v>
+      </c>
+      <c r="Q68">
+        <v>-0.1696562783999997</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.170815252859805</v>
+      </c>
+      <c r="T68">
+        <v>1.597995209179851</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1168288878516763</v>
+      </c>
+      <c r="W68">
+        <v>0.18440612821657</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5310403993258015</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1814852305952699</v>
+      </c>
+      <c r="C69">
+        <v>-4.713054681519486</v>
+      </c>
+      <c r="D69">
+        <v>8.421645318480515</v>
+      </c>
+      <c r="E69">
+        <v>-1.385299999999999</v>
+      </c>
+      <c r="F69">
+        <v>15.0147</v>
+      </c>
+      <c r="G69">
+        <v>1.88</v>
+      </c>
+      <c r="H69">
+        <v>6.01</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.6</v>
+      </c>
+      <c r="K69">
+        <v>0.96</v>
+      </c>
+      <c r="L69">
+        <v>1.64</v>
+      </c>
+      <c r="M69">
+        <v>3.13506936</v>
+      </c>
+      <c r="N69">
+        <v>-1.49506936</v>
+      </c>
+      <c r="O69">
+        <v>-0.3289152592</v>
+      </c>
+      <c r="P69">
+        <v>-1.1661541008</v>
+      </c>
+      <c r="Q69">
+        <v>-0.2061541008000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1748157150676779</v>
+      </c>
+      <c r="T69">
+        <v>1.646419306427725</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1150851731076215</v>
+      </c>
+      <c r="W69">
+        <v>0.1847702158551286</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5231144232164612</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1831852305952699</v>
+      </c>
+      <c r="C70">
+        <v>-5.036311617325117</v>
+      </c>
+      <c r="D70">
+        <v>8.322488382674882</v>
+      </c>
+      <c r="E70">
+        <v>-1.161199999999999</v>
+      </c>
+      <c r="F70">
+        <v>15.2388</v>
+      </c>
+      <c r="G70">
+        <v>1.88</v>
+      </c>
+      <c r="H70">
+        <v>6.01</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.6</v>
+      </c>
+      <c r="K70">
+        <v>0.96</v>
+      </c>
+      <c r="L70">
+        <v>1.64</v>
+      </c>
+      <c r="M70">
+        <v>3.18186144</v>
+      </c>
+      <c r="N70">
+        <v>-1.54186144</v>
+      </c>
+      <c r="O70">
+        <v>-0.3392095168</v>
+      </c>
+      <c r="P70">
+        <v>-1.2026519232</v>
+      </c>
+      <c r="Q70">
+        <v>-0.2426519232</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1790662061635428</v>
+      </c>
+      <c r="T70">
+        <v>1.697869909753591</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1133927440913329</v>
+      </c>
+      <c r="W70">
+        <v>0.1851235950337297</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5154215640515132</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1848852305952699</v>
+      </c>
+      <c r="C71">
+        <v>-5.357260766228785</v>
+      </c>
+      <c r="D71">
+        <v>8.225639233771215</v>
+      </c>
+      <c r="E71">
+        <v>-0.9370999999999992</v>
+      </c>
+      <c r="F71">
+        <v>15.4629</v>
+      </c>
+      <c r="G71">
+        <v>1.88</v>
+      </c>
+      <c r="H71">
+        <v>6.01</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.6</v>
+      </c>
+      <c r="K71">
+        <v>0.96</v>
+      </c>
+      <c r="L71">
+        <v>1.64</v>
+      </c>
+      <c r="M71">
+        <v>3.22865352</v>
+      </c>
+      <c r="N71">
+        <v>-1.58865352</v>
+      </c>
+      <c r="O71">
+        <v>-0.3495037744</v>
+      </c>
+      <c r="P71">
+        <v>-1.2391497456</v>
+      </c>
+      <c r="Q71">
+        <v>-0.2791497455999998</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1835909224913991</v>
+      </c>
+      <c r="T71">
+        <v>1.752639906842417</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.11174937098856</v>
+      </c>
+      <c r="W71">
+        <v>0.1854667313375887</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5079516863116362</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1865852305952699</v>
+      </c>
+      <c r="C72">
+        <v>-5.675981768889782</v>
+      </c>
+      <c r="D72">
+        <v>8.131018231110218</v>
+      </c>
+      <c r="E72">
+        <v>-0.7129999999999992</v>
+      </c>
+      <c r="F72">
+        <v>15.687</v>
+      </c>
+      <c r="G72">
+        <v>1.88</v>
+      </c>
+      <c r="H72">
+        <v>6.01</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.6</v>
+      </c>
+      <c r="K72">
+        <v>0.96</v>
+      </c>
+      <c r="L72">
+        <v>1.64</v>
+      </c>
+      <c r="M72">
+        <v>3.2754456</v>
+      </c>
+      <c r="N72">
+        <v>-1.6354456</v>
+      </c>
+      <c r="O72">
+        <v>-0.359798032</v>
+      </c>
+      <c r="P72">
+        <v>-1.275647568</v>
+      </c>
+      <c r="Q72">
+        <v>-0.3156475680000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1884172865744457</v>
+      </c>
+      <c r="T72">
+        <v>1.811061237070498</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1101529514030091</v>
+      </c>
+      <c r="W72">
+        <v>0.1858000637470517</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5006952336500414</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2100563519805461</v>
+      </c>
+      <c r="C73">
+        <v>-7.014458629550461</v>
+      </c>
+      <c r="D73">
+        <v>7.016641370449537</v>
+      </c>
+      <c r="E73">
+        <v>-0.488900000000001</v>
+      </c>
+      <c r="F73">
+        <v>15.9111</v>
+      </c>
+      <c r="G73">
+        <v>1.88</v>
+      </c>
+      <c r="H73">
+        <v>6.01</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.6</v>
+      </c>
+      <c r="K73">
+        <v>0.96</v>
+      </c>
+      <c r="L73">
+        <v>1.64</v>
+      </c>
+      <c r="M73">
+        <v>3.79957068</v>
+      </c>
+      <c r="N73">
+        <v>-2.159570679999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.4751055495999999</v>
+      </c>
+      <c r="P73">
+        <v>-1.6844651304</v>
+      </c>
+      <c r="Q73">
+        <v>-0.7244651303999996</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1952010598538274</v>
+      </c>
+      <c r="T73">
+        <v>1.89317627276358</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.09495809668686044</v>
+      </c>
+      <c r="W73">
+        <v>0.2161240065111777</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.431627712213002</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2120563519805461</v>
+      </c>
+      <c r="C74">
+        <v>-7.319555848875929</v>
+      </c>
+      <c r="D74">
+        <v>6.935644151124068</v>
+      </c>
+      <c r="E74">
+        <v>-0.264800000000001</v>
+      </c>
+      <c r="F74">
+        <v>16.1352</v>
+      </c>
+      <c r="G74">
+        <v>1.88</v>
+      </c>
+      <c r="H74">
+        <v>6.01</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.6</v>
+      </c>
+      <c r="K74">
+        <v>0.96</v>
+      </c>
+      <c r="L74">
+        <v>1.64</v>
+      </c>
+      <c r="M74">
+        <v>3.853085759999999</v>
+      </c>
+      <c r="N74">
+        <v>-2.213085759999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.4868788671999998</v>
+      </c>
+      <c r="P74">
+        <v>-1.7262068928</v>
+      </c>
+      <c r="Q74">
+        <v>-0.7662068927999997</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2007868119914641</v>
+      </c>
+      <c r="T74">
+        <v>1.960789711076565</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.09363923423287626</v>
+      </c>
+      <c r="W74">
+        <v>0.2164389508651892</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4256328828767103</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2140563519805461</v>
+      </c>
+      <c r="C75">
+        <v>-7.622804411227541</v>
+      </c>
+      <c r="D75">
+        <v>6.856495588772456</v>
+      </c>
+      <c r="E75">
+        <v>-0.04070000000000107</v>
+      </c>
+      <c r="F75">
+        <v>16.3593</v>
+      </c>
+      <c r="G75">
+        <v>1.88</v>
+      </c>
+      <c r="H75">
+        <v>6.01</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.6</v>
+      </c>
+      <c r="K75">
+        <v>0.96</v>
+      </c>
+      <c r="L75">
+        <v>1.64</v>
+      </c>
+      <c r="M75">
+        <v>3.906600839999999</v>
+      </c>
+      <c r="N75">
+        <v>-2.266600839999999</v>
+      </c>
+      <c r="O75">
+        <v>-0.4986521847999998</v>
+      </c>
+      <c r="P75">
+        <v>-1.767948655199999</v>
+      </c>
+      <c r="Q75">
+        <v>-0.8079486551999995</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2067863235467035</v>
+      </c>
+      <c r="T75">
+        <v>2.033411552227549</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.09235650499680947</v>
+      </c>
+      <c r="W75">
+        <v>0.2167452666067619</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4198022954400431</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2160563519805461</v>
+      </c>
+      <c r="C76">
+        <v>-7.924266892313973</v>
+      </c>
+      <c r="D76">
+        <v>6.779133107686024</v>
+      </c>
+      <c r="E76">
+        <v>0.1833999999999989</v>
+      </c>
+      <c r="F76">
+        <v>16.5834</v>
+      </c>
+      <c r="G76">
+        <v>1.88</v>
+      </c>
+      <c r="H76">
+        <v>6.01</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.6</v>
+      </c>
+      <c r="K76">
+        <v>0.96</v>
+      </c>
+      <c r="L76">
+        <v>1.64</v>
+      </c>
+      <c r="M76">
+        <v>3.96011592</v>
+      </c>
+      <c r="N76">
+        <v>-2.32011592</v>
+      </c>
+      <c r="O76">
+        <v>-0.5104255024</v>
+      </c>
+      <c r="P76">
+        <v>-1.8096904176</v>
+      </c>
+      <c r="Q76">
+        <v>-0.8496904175999997</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2132473359908074</v>
+      </c>
+      <c r="T76">
+        <v>2.111619688851686</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0911084441184742</v>
+      </c>
+      <c r="W76">
+        <v>0.2170433035445084</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.41412929144761</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2180563519805461</v>
+      </c>
+      <c r="C77">
+        <v>-8.224003075163681</v>
+      </c>
+      <c r="D77">
+        <v>6.703496924836316</v>
+      </c>
+      <c r="E77">
+        <v>0.4074999999999989</v>
+      </c>
+      <c r="F77">
+        <v>16.8075</v>
+      </c>
+      <c r="G77">
+        <v>1.88</v>
+      </c>
+      <c r="H77">
+        <v>6.01</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.6</v>
+      </c>
+      <c r="K77">
+        <v>0.96</v>
+      </c>
+      <c r="L77">
+        <v>1.64</v>
+      </c>
+      <c r="M77">
+        <v>4.013630999999999</v>
+      </c>
+      <c r="N77">
+        <v>-2.373630999999999</v>
+      </c>
+      <c r="O77">
+        <v>-0.5221988199999998</v>
+      </c>
+      <c r="P77">
+        <v>-1.851432179999999</v>
+      </c>
+      <c r="Q77">
+        <v>-0.8914321799999994</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2202252294304398</v>
+      </c>
+      <c r="T77">
+        <v>2.196084476405753</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08989366486356122</v>
+      </c>
+      <c r="W77">
+        <v>0.2173333928305816</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.408607567561642</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2200563519805462</v>
+      </c>
+      <c r="C78">
+        <v>-8.522070104198402</v>
+      </c>
+      <c r="D78">
+        <v>6.629529895801596</v>
+      </c>
+      <c r="E78">
+        <v>0.6315999999999988</v>
+      </c>
+      <c r="F78">
+        <v>17.0316</v>
+      </c>
+      <c r="G78">
+        <v>1.88</v>
+      </c>
+      <c r="H78">
+        <v>6.01</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.6</v>
+      </c>
+      <c r="K78">
+        <v>0.96</v>
+      </c>
+      <c r="L78">
+        <v>1.64</v>
+      </c>
+      <c r="M78">
+        <v>4.06714608</v>
+      </c>
+      <c r="N78">
+        <v>-2.42714608</v>
+      </c>
+      <c r="O78">
+        <v>-0.5339721376</v>
+      </c>
+      <c r="P78">
+        <v>-1.8931739424</v>
+      </c>
+      <c r="Q78">
+        <v>-0.9331739423999996</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2277846139900414</v>
+      </c>
+      <c r="T78">
+        <v>2.287587996255993</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.08871085348377751</v>
+      </c>
+      <c r="W78">
+        <v>0.2176158481880739</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4032311521989888</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2220563519805461</v>
+      </c>
+      <c r="C79">
+        <v>-8.818522629217622</v>
+      </c>
+      <c r="D79">
+        <v>6.557177370782377</v>
+      </c>
+      <c r="E79">
+        <v>0.8556999999999988</v>
+      </c>
+      <c r="F79">
+        <v>17.2557</v>
+      </c>
+      <c r="G79">
+        <v>1.88</v>
+      </c>
+      <c r="H79">
+        <v>6.01</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.6</v>
+      </c>
+      <c r="K79">
+        <v>0.96</v>
+      </c>
+      <c r="L79">
+        <v>1.64</v>
+      </c>
+      <c r="M79">
+        <v>4.120661159999999</v>
+      </c>
+      <c r="N79">
+        <v>-2.480661159999999</v>
+      </c>
+      <c r="O79">
+        <v>-0.5457454551999998</v>
+      </c>
+      <c r="P79">
+        <v>-1.934915704799999</v>
+      </c>
+      <c r="Q79">
+        <v>-0.9749157047999992</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2360013363374346</v>
+      </c>
+      <c r="T79">
+        <v>2.387048343919298</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08755876447749469</v>
+      </c>
+      <c r="W79">
+        <v>0.2178909670427743</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3979943839886123</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2240563519805461</v>
+      </c>
+      <c r="C80">
+        <v>-9.113412940056421</v>
+      </c>
+      <c r="D80">
+        <v>6.486387059943578</v>
+      </c>
+      <c r="E80">
+        <v>1.079799999999999</v>
+      </c>
+      <c r="F80">
+        <v>17.4798</v>
+      </c>
+      <c r="G80">
+        <v>1.88</v>
+      </c>
+      <c r="H80">
+        <v>6.01</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.6</v>
+      </c>
+      <c r="K80">
+        <v>0.96</v>
+      </c>
+      <c r="L80">
+        <v>1.64</v>
+      </c>
+      <c r="M80">
+        <v>4.17417624</v>
+      </c>
+      <c r="N80">
+        <v>-2.534176239999999</v>
+      </c>
+      <c r="O80">
+        <v>-0.5575187727999998</v>
+      </c>
+      <c r="P80">
+        <v>-1.976657467199999</v>
+      </c>
+      <c r="Q80">
+        <v>-1.016657467199999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2449650334436815</v>
+      </c>
+      <c r="T80">
+        <v>2.495550541370174</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.08643621621496271</v>
+      </c>
+      <c r="W80">
+        <v>0.2181590315678669</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3928918918861941</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2260563519805462</v>
+      </c>
+      <c r="C81">
+        <v>-9.406791092614014</v>
+      </c>
+      <c r="D81">
+        <v>6.417108907385984</v>
+      </c>
+      <c r="E81">
+        <v>1.303899999999999</v>
+      </c>
+      <c r="F81">
+        <v>17.7039</v>
+      </c>
+      <c r="G81">
+        <v>1.88</v>
+      </c>
+      <c r="H81">
+        <v>6.01</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.6</v>
+      </c>
+      <c r="K81">
+        <v>0.96</v>
+      </c>
+      <c r="L81">
+        <v>1.64</v>
+      </c>
+      <c r="M81">
+        <v>4.22769132</v>
+      </c>
+      <c r="N81">
+        <v>-2.58769132</v>
+      </c>
+      <c r="O81">
+        <v>-0.5692920904</v>
+      </c>
+      <c r="P81">
+        <v>-2.0183992296</v>
+      </c>
+      <c r="Q81">
+        <v>-1.0583992296</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2547824159886188</v>
+      </c>
+      <c r="T81">
+        <v>2.614386281435421</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.08534208689578596</v>
+      </c>
+      <c r="W81">
+        <v>0.2184203096492863</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3879185767990271</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2280563519805462</v>
+      </c>
+      <c r="C82">
+        <v>-9.698705026891323</v>
+      </c>
+      <c r="D82">
+        <v>6.349294973108674</v>
+      </c>
+      <c r="E82">
+        <v>1.527999999999999</v>
+      </c>
+      <c r="F82">
+        <v>17.928</v>
+      </c>
+      <c r="G82">
+        <v>1.88</v>
+      </c>
+      <c r="H82">
+        <v>6.01</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.6</v>
+      </c>
+      <c r="K82">
+        <v>0.96</v>
+      </c>
+      <c r="L82">
+        <v>1.64</v>
+      </c>
+      <c r="M82">
+        <v>4.281206399999999</v>
+      </c>
+      <c r="N82">
+        <v>-2.641206399999999</v>
+      </c>
+      <c r="O82">
+        <v>-0.5810654079999998</v>
+      </c>
+      <c r="P82">
+        <v>-2.060140992</v>
+      </c>
+      <c r="Q82">
+        <v>-1.100140992</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2655815367880497</v>
+      </c>
+      <c r="T82">
+        <v>2.745105595507192</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.08427531080958864</v>
+      </c>
+      <c r="W82">
+        <v>0.2186750557786702</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3830695945890393</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2300563519805462</v>
+      </c>
+      <c r="C83">
+        <v>-9.989200677622488</v>
+      </c>
+      <c r="D83">
+        <v>6.282899322377508</v>
+      </c>
+      <c r="E83">
+        <v>1.752099999999999</v>
+      </c>
+      <c r="F83">
+        <v>18.1521</v>
+      </c>
+      <c r="G83">
+        <v>1.88</v>
+      </c>
+      <c r="H83">
+        <v>6.01</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.6</v>
+      </c>
+      <c r="K83">
+        <v>0.96</v>
+      </c>
+      <c r="L83">
+        <v>1.64</v>
+      </c>
+      <c r="M83">
+        <v>4.33472148</v>
+      </c>
+      <c r="N83">
+        <v>-2.69472148</v>
+      </c>
+      <c r="O83">
+        <v>-0.5928387255999999</v>
+      </c>
+      <c r="P83">
+        <v>-2.1018827544</v>
+      </c>
+      <c r="Q83">
+        <v>-1.1418827544</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2775174071453155</v>
+      </c>
+      <c r="T83">
+        <v>2.889584837375992</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.08323487487366779</v>
+      </c>
+      <c r="W83">
+        <v>0.2189235118801681</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3783403403348535</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2320563519805462</v>
+      </c>
+      <c r="C84">
+        <v>-10.2783220780369</v>
+      </c>
+      <c r="D84">
+        <v>6.217877921963099</v>
+      </c>
+      <c r="E84">
+        <v>1.976199999999999</v>
+      </c>
+      <c r="F84">
+        <v>18.3762</v>
+      </c>
+      <c r="G84">
+        <v>1.88</v>
+      </c>
+      <c r="H84">
+        <v>6.01</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.6</v>
+      </c>
+      <c r="K84">
+        <v>0.96</v>
+      </c>
+      <c r="L84">
+        <v>1.64</v>
+      </c>
+      <c r="M84">
+        <v>4.388236559999999</v>
+      </c>
+      <c r="N84">
+        <v>-2.748236559999999</v>
+      </c>
+      <c r="O84">
+        <v>-0.6046120431999998</v>
+      </c>
+      <c r="P84">
+        <v>-2.143624516799999</v>
+      </c>
+      <c r="Q84">
+        <v>-1.183624516799999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2907794853200553</v>
+      </c>
+      <c r="T84">
+        <v>3.050117328341325</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.08221981542398893</v>
+      </c>
+      <c r="W84">
+        <v>0.2191659080767515</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3737264337454042</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2340563519805461</v>
+      </c>
+      <c r="C85">
+        <v>-10.56611145724422</v>
+      </c>
+      <c r="D85">
+        <v>6.154188542755781</v>
+      </c>
+      <c r="E85">
+        <v>2.200299999999999</v>
+      </c>
+      <c r="F85">
+        <v>18.6003</v>
+      </c>
+      <c r="G85">
+        <v>1.88</v>
+      </c>
+      <c r="H85">
+        <v>6.01</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.6</v>
+      </c>
+      <c r="K85">
+        <v>0.96</v>
+      </c>
+      <c r="L85">
+        <v>1.64</v>
+      </c>
+      <c r="M85">
+        <v>4.44175164</v>
+      </c>
+      <c r="N85">
+        <v>-2.80175164</v>
+      </c>
+      <c r="O85">
+        <v>-0.6163853607999999</v>
+      </c>
+      <c r="P85">
+        <v>-2.1853662792</v>
+      </c>
+      <c r="Q85">
+        <v>-1.2253662792</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3056018079859409</v>
+      </c>
+      <c r="T85">
+        <v>3.229535994714344</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.08122921523815772</v>
+      </c>
+      <c r="W85">
+        <v>0.219402463401128</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3692237056279897</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2360563519805461</v>
+      </c>
+      <c r="C86">
+        <v>-10.85260933169505</v>
+      </c>
+      <c r="D86">
+        <v>6.09179066830495</v>
+      </c>
+      <c r="E86">
+        <v>2.424399999999999</v>
+      </c>
+      <c r="F86">
+        <v>18.8244</v>
+      </c>
+      <c r="G86">
+        <v>1.88</v>
+      </c>
+      <c r="H86">
+        <v>6.01</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.6</v>
+      </c>
+      <c r="K86">
+        <v>0.96</v>
+      </c>
+      <c r="L86">
+        <v>1.64</v>
+      </c>
+      <c r="M86">
+        <v>4.495266719999999</v>
+      </c>
+      <c r="N86">
+        <v>-2.855266719999999</v>
+      </c>
+      <c r="O86">
+        <v>-0.6281586783999998</v>
+      </c>
+      <c r="P86">
+        <v>-2.227108041599999</v>
+      </c>
+      <c r="Q86">
+        <v>-1.267108041599999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3222769209850621</v>
+      </c>
+      <c r="T86">
+        <v>3.431381994383989</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.08026220077103681</v>
+      </c>
+      <c r="W86">
+        <v>0.2196333864558764</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3648281853228946</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2380563519805461</v>
+      </c>
+      <c r="C87">
+        <v>-11.1378545911335</v>
+      </c>
+      <c r="D87">
+        <v>6.030645408866496</v>
+      </c>
+      <c r="E87">
+        <v>2.648499999999999</v>
+      </c>
+      <c r="F87">
+        <v>19.0485</v>
+      </c>
+      <c r="G87">
+        <v>1.88</v>
+      </c>
+      <c r="H87">
+        <v>6.01</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.6</v>
+      </c>
+      <c r="K87">
+        <v>0.96</v>
+      </c>
+      <c r="L87">
+        <v>1.64</v>
+      </c>
+      <c r="M87">
+        <v>4.5487818</v>
+      </c>
+      <c r="N87">
+        <v>-2.908781799999999</v>
+      </c>
+      <c r="O87">
+        <v>-0.6399319959999998</v>
+      </c>
+      <c r="P87">
+        <v>-2.268849803999999</v>
+      </c>
+      <c r="Q87">
+        <v>-1.308849803999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3411753823840663</v>
+      </c>
+      <c r="T87">
+        <v>3.660140794009588</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07931793958549518</v>
+      </c>
+      <c r="W87">
+        <v>0.2198588760269838</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3605360890249781</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2400563519805461</v>
+      </c>
+      <c r="C88">
+        <v>-11.42188457942474</v>
+      </c>
+      <c r="D88">
+        <v>5.970715420575251</v>
+      </c>
+      <c r="E88">
+        <v>2.872599999999998</v>
+      </c>
+      <c r="F88">
+        <v>19.2726</v>
+      </c>
+      <c r="G88">
+        <v>1.88</v>
+      </c>
+      <c r="H88">
+        <v>6.01</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.6</v>
+      </c>
+      <c r="K88">
+        <v>0.96</v>
+      </c>
+      <c r="L88">
+        <v>1.64</v>
+      </c>
+      <c r="M88">
+        <v>4.60229688</v>
+      </c>
+      <c r="N88">
+        <v>-2.96229688</v>
+      </c>
+      <c r="O88">
+        <v>-0.6517053135999999</v>
+      </c>
+      <c r="P88">
+        <v>-2.3105915664</v>
+      </c>
+      <c r="Q88">
+        <v>-1.3505915664</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3627736239829281</v>
+      </c>
+      <c r="T88">
+        <v>3.921579422153131</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07839563796240802</v>
+      </c>
+      <c r="W88">
+        <v>0.220079121654577</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3563438089200365</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2420563519805461</v>
+      </c>
+      <c r="C89">
+        <v>-11.70473517061066</v>
+      </c>
+      <c r="D89">
+        <v>5.911964829389333</v>
+      </c>
+      <c r="E89">
+        <v>3.096699999999998</v>
+      </c>
+      <c r="F89">
+        <v>19.4967</v>
+      </c>
+      <c r="G89">
+        <v>1.88</v>
+      </c>
+      <c r="H89">
+        <v>6.01</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.6</v>
+      </c>
+      <c r="K89">
+        <v>0.96</v>
+      </c>
+      <c r="L89">
+        <v>1.64</v>
+      </c>
+      <c r="M89">
+        <v>4.655811959999999</v>
+      </c>
+      <c r="N89">
+        <v>-3.015811959999999</v>
+      </c>
+      <c r="O89">
+        <v>-0.6634786311999998</v>
+      </c>
+      <c r="P89">
+        <v>-2.352333328799999</v>
+      </c>
+      <c r="Q89">
+        <v>-1.392333328799999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3876946719816149</v>
+      </c>
+      <c r="T89">
+        <v>4.223239377703371</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07749453867548381</v>
+      </c>
+      <c r="W89">
+        <v>0.2202943041642945</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3522479030703809</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2440563519805461</v>
+      </c>
+      <c r="C90">
+        <v>-11.98644084051899</v>
+      </c>
+      <c r="D90">
+        <v>5.854359159481002</v>
+      </c>
+      <c r="E90">
+        <v>3.320799999999998</v>
+      </c>
+      <c r="F90">
+        <v>19.7208</v>
+      </c>
+      <c r="G90">
+        <v>1.88</v>
+      </c>
+      <c r="H90">
+        <v>6.01</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.6</v>
+      </c>
+      <c r="K90">
+        <v>0.96</v>
+      </c>
+      <c r="L90">
+        <v>1.64</v>
+      </c>
+      <c r="M90">
+        <v>4.70932704</v>
+      </c>
+      <c r="N90">
+        <v>-3.06932704</v>
+      </c>
+      <c r="O90">
+        <v>-0.6752519487999999</v>
+      </c>
+      <c r="P90">
+        <v>-2.3940750912</v>
+      </c>
+      <c r="Q90">
+        <v>-1.4340750912</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4167692279800828</v>
+      </c>
+      <c r="T90">
+        <v>4.575175992511986</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07661391891780785</v>
+      </c>
+      <c r="W90">
+        <v>0.2205045961624275</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3482450859900357</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2460563519805462</v>
+      </c>
+      <c r="C91">
+        <v>-12.26703473422634</v>
+      </c>
+      <c r="D91">
+        <v>5.797865265773654</v>
+      </c>
+      <c r="E91">
+        <v>3.544899999999998</v>
+      </c>
+      <c r="F91">
+        <v>19.9449</v>
+      </c>
+      <c r="G91">
+        <v>1.88</v>
+      </c>
+      <c r="H91">
+        <v>6.01</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.6</v>
+      </c>
+      <c r="K91">
+        <v>0.96</v>
+      </c>
+      <c r="L91">
+        <v>1.64</v>
+      </c>
+      <c r="M91">
+        <v>4.762842119999999</v>
+      </c>
+      <c r="N91">
+        <v>-3.122842119999999</v>
+      </c>
+      <c r="O91">
+        <v>-0.6870252663999998</v>
+      </c>
+      <c r="P91">
+        <v>-2.4358168536</v>
+      </c>
+      <c r="Q91">
+        <v>-1.4758168536</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4511300668873631</v>
+      </c>
+      <c r="T91">
+        <v>4.991101082740348</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07575308836816956</v>
+      </c>
+      <c r="W91">
+        <v>0.2207101624976811</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3443322198553163</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2480563519805462</v>
+      </c>
+      <c r="C92">
+        <v>-12.54654872965252</v>
+      </c>
+      <c r="D92">
+        <v>5.742451270347481</v>
+      </c>
+      <c r="E92">
+        <v>3.768999999999998</v>
+      </c>
+      <c r="F92">
+        <v>20.169</v>
+      </c>
+      <c r="G92">
+        <v>1.88</v>
+      </c>
+      <c r="H92">
+        <v>6.01</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.6</v>
+      </c>
+      <c r="K92">
+        <v>0.96</v>
+      </c>
+      <c r="L92">
+        <v>1.64</v>
+      </c>
+      <c r="M92">
+        <v>4.8163572</v>
+      </c>
+      <c r="N92">
+        <v>-3.1763572</v>
+      </c>
+      <c r="O92">
+        <v>-0.6987985839999999</v>
+      </c>
+      <c r="P92">
+        <v>-2.477558616</v>
+      </c>
+      <c r="Q92">
+        <v>-1.517558616</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4923630735760995</v>
+      </c>
+      <c r="T92">
+        <v>5.490211191014384</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07491138738630101</v>
+      </c>
+      <c r="W92">
+        <v>0.2209111606921513</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3405063063013682</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2500563519805461</v>
+      </c>
+      <c r="C93">
+        <v>-12.82501349754244</v>
+      </c>
+      <c r="D93">
+        <v>5.688086502457557</v>
+      </c>
+      <c r="E93">
+        <v>3.993099999999998</v>
+      </c>
+      <c r="F93">
+        <v>20.3931</v>
+      </c>
+      <c r="G93">
+        <v>1.88</v>
+      </c>
+      <c r="H93">
+        <v>6.01</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.6</v>
+      </c>
+      <c r="K93">
+        <v>0.96</v>
+      </c>
+      <c r="L93">
+        <v>1.64</v>
+      </c>
+      <c r="M93">
+        <v>4.869872279999999</v>
+      </c>
+      <c r="N93">
+        <v>-3.229872279999999</v>
+      </c>
+      <c r="O93">
+        <v>-0.7105719015999998</v>
+      </c>
+      <c r="P93">
+        <v>-2.519300378399999</v>
+      </c>
+      <c r="Q93">
+        <v>-1.559300378399999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5427589706401106</v>
+      </c>
+      <c r="T93">
+        <v>6.10023465668265</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07408818532711089</v>
+      </c>
+      <c r="W93">
+        <v>0.2211077413438859</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.336764478759595</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2520563519805462</v>
+      </c>
+      <c r="C94">
+        <v>-13.10245855807294</v>
+      </c>
+      <c r="D94">
+        <v>5.634741441927059</v>
+      </c>
+      <c r="E94">
+        <v>4.217199999999998</v>
+      </c>
+      <c r="F94">
+        <v>20.6172</v>
+      </c>
+      <c r="G94">
+        <v>1.88</v>
+      </c>
+      <c r="H94">
+        <v>6.01</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.6</v>
+      </c>
+      <c r="K94">
+        <v>0.96</v>
+      </c>
+      <c r="L94">
+        <v>1.64</v>
+      </c>
+      <c r="M94">
+        <v>4.92338736</v>
+      </c>
+      <c r="N94">
+        <v>-3.283387359999999</v>
+      </c>
+      <c r="O94">
+        <v>-0.7223452191999998</v>
+      </c>
+      <c r="P94">
+        <v>-2.5610421408</v>
+      </c>
+      <c r="Q94">
+        <v>-1.6010421408</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6057538419701245</v>
+      </c>
+      <c r="T94">
+        <v>6.862763988767983</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07328287896485969</v>
+      </c>
+      <c r="W94">
+        <v>0.2213000485031915</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3331039952948167</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2540563519805462</v>
+      </c>
+      <c r="C95">
+        <v>-13.37891233430377</v>
+      </c>
+      <c r="D95">
+        <v>5.58238766569623</v>
+      </c>
+      <c r="E95">
+        <v>4.441299999999998</v>
+      </c>
+      <c r="F95">
+        <v>20.8413</v>
+      </c>
+      <c r="G95">
+        <v>1.88</v>
+      </c>
+      <c r="H95">
+        <v>6.01</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.6</v>
+      </c>
+      <c r="K95">
+        <v>0.96</v>
+      </c>
+      <c r="L95">
+        <v>1.64</v>
+      </c>
+      <c r="M95">
+        <v>4.97690244</v>
+      </c>
+      <c r="N95">
+        <v>-3.33690244</v>
+      </c>
+      <c r="O95">
+        <v>-0.7341185367999999</v>
+      </c>
+      <c r="P95">
+        <v>-2.6027839032</v>
+      </c>
+      <c r="Q95">
+        <v>-1.6427839032</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6867472479658567</v>
+      </c>
+      <c r="T95">
+        <v>7.843158844306267</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07249489101900097</v>
+      </c>
+      <c r="W95">
+        <v>0.2214882200246626</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3295222319045499</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2560563519805462</v>
+      </c>
+      <c r="C96">
+        <v>-13.65440220267637</v>
+      </c>
+      <c r="D96">
+        <v>5.530997797323625</v>
+      </c>
+      <c r="E96">
+        <v>4.665399999999998</v>
+      </c>
+      <c r="F96">
+        <v>21.0654</v>
+      </c>
+      <c r="G96">
+        <v>1.88</v>
+      </c>
+      <c r="H96">
+        <v>6.01</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.6</v>
+      </c>
+      <c r="K96">
+        <v>0.96</v>
+      </c>
+      <c r="L96">
+        <v>1.64</v>
+      </c>
+      <c r="M96">
+        <v>5.030417519999999</v>
+      </c>
+      <c r="N96">
+        <v>-3.390417519999999</v>
+      </c>
+      <c r="O96">
+        <v>-0.7458918543999998</v>
+      </c>
+      <c r="P96">
+        <v>-2.644525665599999</v>
+      </c>
+      <c r="Q96">
+        <v>-1.684525665599999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7947384559601662</v>
+      </c>
+      <c r="T96">
+        <v>9.150351985023979</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.071723668774118</v>
+      </c>
+      <c r="W96">
+        <v>0.2216723878967407</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3260166762459908</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2580563519805462</v>
+      </c>
+      <c r="C97">
+        <v>-13.92895454074879</v>
+      </c>
+      <c r="D97">
+        <v>5.48054545925121</v>
+      </c>
+      <c r="E97">
+        <v>4.889499999999998</v>
+      </c>
+      <c r="F97">
+        <v>21.2895</v>
+      </c>
+      <c r="G97">
+        <v>1.88</v>
+      </c>
+      <c r="H97">
+        <v>6.01</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.6</v>
+      </c>
+      <c r="K97">
+        <v>0.96</v>
+      </c>
+      <c r="L97">
+        <v>1.64</v>
+      </c>
+      <c r="M97">
+        <v>5.0839326</v>
+      </c>
+      <c r="N97">
+        <v>-3.4439326</v>
+      </c>
+      <c r="O97">
+        <v>-0.7576651719999999</v>
+      </c>
+      <c r="P97">
+        <v>-2.686267428</v>
+      </c>
+      <c r="Q97">
+        <v>-1.726267428</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9459261471522</v>
+      </c>
+      <c r="T97">
+        <v>10.98042238202878</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.07096868278702201</v>
+      </c>
+      <c r="W97">
+        <v>0.2218526785504592</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.322584921759191</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2600563519805461</v>
+      </c>
+      <c r="C98">
+        <v>-14.20259477234162</v>
+      </c>
+      <c r="D98">
+        <v>5.431005227658375</v>
+      </c>
+      <c r="E98">
+        <v>5.113599999999998</v>
+      </c>
+      <c r="F98">
+        <v>21.5136</v>
+      </c>
+      <c r="G98">
+        <v>1.88</v>
+      </c>
+      <c r="H98">
+        <v>6.01</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.6</v>
+      </c>
+      <c r="K98">
+        <v>0.96</v>
+      </c>
+      <c r="L98">
+        <v>1.64</v>
+      </c>
+      <c r="M98">
+        <v>5.137447679999999</v>
+      </c>
+      <c r="N98">
+        <v>-3.497447679999999</v>
+      </c>
+      <c r="O98">
+        <v>-0.7694384895999998</v>
+      </c>
+      <c r="P98">
+        <v>-2.728009190399999</v>
+      </c>
+      <c r="Q98">
+        <v>-1.768009190399999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.172707683940247</v>
+      </c>
+      <c r="T98">
+        <v>13.72552797753595</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0702294256746572</v>
+      </c>
+      <c r="W98">
+        <v>0.2220292131488919</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3192246621575328</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2620563519805461</v>
+      </c>
+      <c r="C99">
+        <v>-14.47534741025745</v>
+      </c>
+      <c r="D99">
+        <v>5.382352589742553</v>
+      </c>
+      <c r="E99">
+        <v>5.337699999999998</v>
+      </c>
+      <c r="F99">
+        <v>21.7377</v>
+      </c>
+      <c r="G99">
+        <v>1.88</v>
+      </c>
+      <c r="H99">
+        <v>6.01</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.6</v>
+      </c>
+      <c r="K99">
+        <v>0.96</v>
+      </c>
+      <c r="L99">
+        <v>1.64</v>
+      </c>
+      <c r="M99">
+        <v>5.19096276</v>
+      </c>
+      <c r="N99">
+        <v>-3.55096276</v>
+      </c>
+      <c r="O99">
+        <v>-0.7812118071999999</v>
+      </c>
+      <c r="P99">
+        <v>-2.769750952799999</v>
+      </c>
+      <c r="Q99">
+        <v>-1.8097509528</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.55067691192033</v>
+      </c>
+      <c r="T99">
+        <v>18.30070397004793</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06950541097698032</v>
+      </c>
+      <c r="W99">
+        <v>0.2222021078586971</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3159336862590014</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2640563519805461</v>
+      </c>
+      <c r="C100">
+        <v>-14.74723609672438</v>
+      </c>
+      <c r="D100">
+        <v>5.334563903275613</v>
+      </c>
+      <c r="E100">
+        <v>5.561799999999998</v>
+      </c>
+      <c r="F100">
+        <v>21.9618</v>
+      </c>
+      <c r="G100">
+        <v>1.88</v>
+      </c>
+      <c r="H100">
+        <v>6.01</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.6</v>
+      </c>
+      <c r="K100">
+        <v>0.96</v>
+      </c>
+      <c r="L100">
+        <v>1.64</v>
+      </c>
+      <c r="M100">
+        <v>5.244477839999999</v>
+      </c>
+      <c r="N100">
+        <v>-3.604477839999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.7929851247999998</v>
+      </c>
+      <c r="P100">
+        <v>-2.811492715199999</v>
+      </c>
+      <c r="Q100">
+        <v>-1.851492715199999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.306615367880495</v>
+      </c>
+      <c r="T100">
+        <v>27.45105595507189</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06879617208946012</v>
+      </c>
+      <c r="W100">
+        <v>0.2223714741050369</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3127098731339096</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2660563519805461</v>
+      </c>
+      <c r="C101">
+        <v>-15.01828364170418</v>
+      </c>
+      <c r="D101">
+        <v>5.287616358295813</v>
+      </c>
+      <c r="E101">
+        <v>5.785899999999998</v>
+      </c>
+      <c r="F101">
+        <v>22.1859</v>
+      </c>
+      <c r="G101">
+        <v>1.88</v>
+      </c>
+      <c r="H101">
+        <v>6.01</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.6</v>
+      </c>
+      <c r="K101">
+        <v>0.96</v>
+      </c>
+      <c r="L101">
+        <v>1.64</v>
+      </c>
+      <c r="M101">
+        <v>5.29799292</v>
+      </c>
+      <c r="N101">
+        <v>-3.657992919999999</v>
+      </c>
+      <c r="O101">
+        <v>-0.8047584423999998</v>
+      </c>
+      <c r="P101">
+        <v>-2.8532344776</v>
+      </c>
+      <c r="Q101">
+        <v>-1.8932344776</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.574430735760991</v>
+      </c>
+      <c r="T101">
+        <v>54.90211191014379</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06810126126027365</v>
+      </c>
+      <c r="W101">
+        <v>0.2225374188110467</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3095511875466984</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
